--- a/cs_full_phase_results.xlsx
+++ b/cs_full_phase_results.xlsx
@@ -23,8 +23,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase4_best_params" sheetId="14" state="visible" r:id="rId14"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase5_stack" sheetId="15" state="visible" r:id="rId15"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase6_SMOGN" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Final_test_R2_by_regime" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Final_gap_by_regime" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase7_ANN" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase9_Stack_SE" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase10_CV_shootout" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase11_push" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Final_test_R2_by_regime" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Final_gap_by_regime" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1216,7 +1220,7 @@
         <v>100</v>
       </c>
       <c r="Y2" t="n">
-        <v>78.20801711082458</v>
+        <v>76.4141640663147</v>
       </c>
     </row>
     <row r="3">
@@ -1299,7 +1303,7 @@
         <v>100</v>
       </c>
       <c r="Y3" t="n">
-        <v>78.20801711082458</v>
+        <v>76.4141640663147</v>
       </c>
     </row>
     <row r="4">
@@ -1382,7 +1386,7 @@
         <v>100</v>
       </c>
       <c r="Y4" t="n">
-        <v>52.84174370765686</v>
+        <v>51.67198491096497</v>
       </c>
     </row>
     <row r="5">
@@ -1465,7 +1469,7 @@
         <v>100</v>
       </c>
       <c r="Y5" t="n">
-        <v>52.84174370765686</v>
+        <v>51.67198491096497</v>
       </c>
     </row>
     <row r="6">
@@ -1548,7 +1552,7 @@
         <v>100</v>
       </c>
       <c r="Y6" t="n">
-        <v>57.80050492286682</v>
+        <v>57.15808701515198</v>
       </c>
     </row>
     <row r="7">
@@ -1631,7 +1635,7 @@
         <v>100</v>
       </c>
       <c r="Y7" t="n">
-        <v>57.80050492286682</v>
+        <v>57.15808701515198</v>
       </c>
     </row>
     <row r="8">
@@ -1714,7 +1718,7 @@
         <v>100</v>
       </c>
       <c r="Y8" t="n">
-        <v>50.46114706993103</v>
+        <v>49.68790769577026</v>
       </c>
     </row>
     <row r="9">
@@ -1797,7 +1801,7 @@
         <v>100</v>
       </c>
       <c r="Y9" t="n">
-        <v>50.46114706993103</v>
+        <v>49.68790769577026</v>
       </c>
     </row>
     <row r="10">
@@ -1880,7 +1884,7 @@
         <v>100</v>
       </c>
       <c r="Y10" t="n">
-        <v>19.73914432525635</v>
+        <v>19.94060683250427</v>
       </c>
     </row>
     <row r="11">
@@ -1963,7 +1967,7 @@
         <v>100</v>
       </c>
       <c r="Y11" t="n">
-        <v>19.73914432525635</v>
+        <v>19.94060683250427</v>
       </c>
     </row>
     <row r="12">
@@ -2046,7 +2050,7 @@
         <v>100</v>
       </c>
       <c r="Y12" t="n">
-        <v>22.34944295883179</v>
+        <v>22.17919397354126</v>
       </c>
     </row>
     <row r="13">
@@ -2129,7 +2133,7 @@
         <v>100</v>
       </c>
       <c r="Y13" t="n">
-        <v>22.34944295883179</v>
+        <v>22.17919397354126</v>
       </c>
     </row>
     <row r="14">
@@ -2212,7 +2216,7 @@
         <v>100</v>
       </c>
       <c r="Y14" t="n">
-        <v>68.52683687210083</v>
+        <v>68.63058495521545</v>
       </c>
     </row>
     <row r="15">
@@ -2295,7 +2299,7 @@
         <v>100</v>
       </c>
       <c r="Y15" t="n">
-        <v>68.52683687210083</v>
+        <v>68.63058495521545</v>
       </c>
     </row>
     <row r="16">
@@ -2378,7 +2382,7 @@
         <v>100</v>
       </c>
       <c r="Y16" t="n">
-        <v>54.97517395019531</v>
+        <v>57.69789409637451</v>
       </c>
     </row>
     <row r="17">
@@ -2461,7 +2465,7 @@
         <v>100</v>
       </c>
       <c r="Y17" t="n">
-        <v>54.97517395019531</v>
+        <v>57.69789409637451</v>
       </c>
     </row>
     <row r="18">
@@ -2544,7 +2548,7 @@
         <v>100</v>
       </c>
       <c r="Y18" t="n">
-        <v>55.20129036903381</v>
+        <v>56.37726998329163</v>
       </c>
     </row>
     <row r="19">
@@ -2627,7 +2631,7 @@
         <v>100</v>
       </c>
       <c r="Y19" t="n">
-        <v>55.20129036903381</v>
+        <v>56.37726998329163</v>
       </c>
     </row>
     <row r="20">
@@ -2710,7 +2714,7 @@
         <v>100</v>
       </c>
       <c r="Y20" t="n">
-        <v>40.54985690116882</v>
+        <v>39.44781517982483</v>
       </c>
     </row>
     <row r="21">
@@ -2793,7 +2797,7 @@
         <v>100</v>
       </c>
       <c r="Y21" t="n">
-        <v>40.54985690116882</v>
+        <v>39.44781517982483</v>
       </c>
     </row>
     <row r="22">
@@ -2876,7 +2880,7 @@
         <v>100</v>
       </c>
       <c r="Y22" t="n">
-        <v>14.89971995353699</v>
+        <v>15.06471395492554</v>
       </c>
     </row>
     <row r="23">
@@ -2959,7 +2963,7 @@
         <v>100</v>
       </c>
       <c r="Y23" t="n">
-        <v>14.89971995353699</v>
+        <v>15.06471395492554</v>
       </c>
     </row>
     <row r="24">
@@ -3042,7 +3046,7 @@
         <v>100</v>
       </c>
       <c r="Y24" t="n">
-        <v>26.61227416992188</v>
+        <v>26.81860876083374</v>
       </c>
     </row>
     <row r="25">
@@ -3125,7 +3129,7 @@
         <v>100</v>
       </c>
       <c r="Y25" t="n">
-        <v>26.61227416992188</v>
+        <v>26.81860876083374</v>
       </c>
     </row>
   </sheetData>
@@ -3792,7 +3796,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W45"/>
+  <dimension ref="A1:W49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4689,61 +4693,61 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.8978733015162615</v>
+        <v>0.8978185529822343</v>
       </c>
       <c r="C12" t="n">
-        <v>0.04354931923736104</v>
+        <v>0.04347696707168115</v>
       </c>
       <c r="D12" t="n">
-        <v>3.227258217844066</v>
+        <v>3.228832938257832</v>
       </c>
       <c r="E12" t="n">
-        <v>0.7148016367510256</v>
+        <v>0.7127909487915964</v>
       </c>
       <c r="F12" t="n">
-        <v>4.734169134906917</v>
+        <v>4.736312201892869</v>
       </c>
       <c r="G12" t="n">
-        <v>0.9903583794335099</v>
+        <v>0.9876790222048267</v>
       </c>
       <c r="H12" t="n">
-        <v>0.5553858593751115</v>
+        <v>0.55543316537026</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1011179653017363</v>
+        <v>0.101148488996815</v>
       </c>
       <c r="J12" t="n">
-        <v>6.603683437752761</v>
+        <v>6.603456439484204</v>
       </c>
       <c r="K12" t="n">
-        <v>0.7165007956172348</v>
+        <v>0.7168627248868136</v>
       </c>
       <c r="L12" t="n">
-        <v>9.28601016559311</v>
+        <v>9.285559161104946</v>
       </c>
       <c r="M12" t="n">
-        <v>1.194473456778372</v>
+        <v>1.19524770544198</v>
       </c>
       <c r="N12" t="n">
-        <v>0.5935533012047602</v>
+        <v>0.5935778340706519</v>
       </c>
       <c r="O12" t="n">
-        <v>0.09057082321489239</v>
+        <v>0.0905491410756875</v>
       </c>
       <c r="P12" t="n">
-        <v>6.597058706652445</v>
+        <v>6.596481851984131</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.7236931729206104</v>
+        <v>0.7242427141423494</v>
       </c>
       <c r="R12" t="n">
-        <v>9.328792220863823</v>
+        <v>9.328586671177071</v>
       </c>
       <c r="S12" t="n">
-        <v>1.379017294495553</v>
+        <v>1.379192222421037</v>
       </c>
       <c r="T12" t="n">
-        <v>0.3043200003115013</v>
+        <v>0.3042407189115824</v>
       </c>
       <c r="U12" t="inlineStr">
         <is>
@@ -4756,7 +4760,7 @@
         </is>
       </c>
       <c r="W12" t="n">
-        <v>0.305310673273094</v>
+        <v>0.3059223313571385</v>
       </c>
     </row>
     <row r="13">
@@ -4766,61 +4770,61 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.9384878517117368</v>
+        <v>0.9381415109252176</v>
       </c>
       <c r="C13" t="n">
-        <v>0.01513075275658635</v>
+        <v>0.01461888954364404</v>
       </c>
       <c r="D13" t="n">
-        <v>2.349250938718222</v>
+        <v>2.357165739157963</v>
       </c>
       <c r="E13" t="n">
-        <v>0.3747245187212083</v>
+        <v>0.3623025756929473</v>
       </c>
       <c r="F13" t="n">
-        <v>3.578932252120571</v>
+        <v>3.591031698708794</v>
       </c>
       <c r="G13" t="n">
-        <v>0.5423755804228233</v>
+        <v>0.5239481720002365</v>
       </c>
       <c r="H13" t="n">
-        <v>0.305310673273094</v>
+        <v>0.3059223313571385</v>
       </c>
       <c r="I13" t="n">
-        <v>0.09012919363243456</v>
+        <v>0.08990734899177447</v>
       </c>
       <c r="J13" t="n">
-        <v>9.505085143397842</v>
+        <v>9.501520003159998</v>
       </c>
       <c r="K13" t="n">
-        <v>2.260831303682733</v>
+        <v>2.255015025739549</v>
       </c>
       <c r="L13" t="n">
-        <v>13.12972068045537</v>
+        <v>13.12206149189417</v>
       </c>
       <c r="M13" t="n">
-        <v>3.244182892891627</v>
+        <v>3.232158457506632</v>
       </c>
       <c r="N13" t="n">
-        <v>0.3857847941304072</v>
+        <v>0.385196506068637</v>
       </c>
       <c r="O13" t="n">
-        <v>0.1996278162474173</v>
+        <v>0.200195910421472</v>
       </c>
       <c r="P13" t="n">
-        <v>7.710818079998544</v>
+        <v>7.715357870246355</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.737706638836672</v>
+        <v>1.736872850185075</v>
       </c>
       <c r="R13" t="n">
-        <v>11.4063995809167</v>
+        <v>11.41027320966973</v>
       </c>
       <c r="S13" t="n">
-        <v>3.014366288212004</v>
+        <v>3.013365610944872</v>
       </c>
       <c r="T13" t="n">
-        <v>0.5527030575813296</v>
+        <v>0.5529450048565805</v>
       </c>
       <c r="U13" t="inlineStr">
         <is>
@@ -4833,7 +4837,7 @@
         </is>
       </c>
       <c r="W13" t="n">
-        <v>0.305310673273094</v>
+        <v>0.3059223313571385</v>
       </c>
     </row>
     <row r="14">
@@ -5151,61 +5155,61 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.9654613255628658</v>
+        <v>0.9353481832657935</v>
       </c>
       <c r="C18" t="n">
-        <v>0.01099849695833136</v>
+        <v>0.01526118424160498</v>
       </c>
       <c r="D18" t="n">
-        <v>1.598676528637349</v>
+        <v>2.492333593931541</v>
       </c>
       <c r="E18" t="n">
-        <v>0.209423706831151</v>
+        <v>0.2236335978736582</v>
       </c>
       <c r="F18" t="n">
-        <v>2.776869334698574</v>
+        <v>3.822116854209696</v>
       </c>
       <c r="G18" t="n">
-        <v>0.4427246331091401</v>
+        <v>0.433143019497188</v>
       </c>
       <c r="H18" t="n">
-        <v>0.6785154571194612</v>
+        <v>0.6671486874400689</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1072039005800842</v>
+        <v>0.1083921391429847</v>
       </c>
       <c r="J18" t="n">
-        <v>5.480031991826586</v>
+        <v>5.713627537434665</v>
       </c>
       <c r="K18" t="n">
-        <v>0.6492623164979786</v>
+        <v>0.6719877708648641</v>
       </c>
       <c r="L18" t="n">
-        <v>7.831035664721139</v>
+        <v>7.971828666551724</v>
       </c>
       <c r="M18" t="n">
-        <v>1.256466607918354</v>
+        <v>1.250484616867678</v>
       </c>
       <c r="N18" t="n">
-        <v>0.6977481385930541</v>
+        <v>0.6797620895934489</v>
       </c>
       <c r="O18" t="n">
-        <v>0.093390849625536</v>
+        <v>0.09659693388019659</v>
       </c>
       <c r="P18" t="n">
-        <v>5.520671731974281</v>
+        <v>5.783134917040189</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.6597746097653849</v>
+        <v>0.6928062842165703</v>
       </c>
       <c r="R18" t="n">
-        <v>7.965210592879435</v>
+        <v>8.201195433368618</v>
       </c>
       <c r="S18" t="n">
-        <v>1.313978810343274</v>
+        <v>1.303212565729106</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2677131869698117</v>
+        <v>0.2555860936723446</v>
       </c>
       <c r="U18" t="inlineStr">
         <is>
@@ -5218,7 +5222,7 @@
         </is>
       </c>
       <c r="W18" t="n">
-        <v>0.4860327627622528</v>
+        <v>0.4844628548595775</v>
       </c>
     </row>
     <row r="19">
@@ -5228,61 +5232,61 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.9705875927978896</v>
+        <v>0.9455634610237889</v>
       </c>
       <c r="C19" t="n">
-        <v>0.01192338159101609</v>
+        <v>0.01632833395300252</v>
       </c>
       <c r="D19" t="n">
-        <v>1.430205808478588</v>
+        <v>2.224633279735309</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3354928134464878</v>
+        <v>0.3531374158462773</v>
       </c>
       <c r="F19" t="n">
-        <v>2.428309957409171</v>
+        <v>3.350024415890302</v>
       </c>
       <c r="G19" t="n">
-        <v>0.5802568756561601</v>
+        <v>0.6098193975392179</v>
       </c>
       <c r="H19" t="n">
-        <v>0.4860327627622528</v>
+        <v>0.4844628548595775</v>
       </c>
       <c r="I19" t="n">
-        <v>0.04156134132379476</v>
+        <v>0.04643833666270597</v>
       </c>
       <c r="J19" t="n">
-        <v>8.081629961970981</v>
+        <v>8.143488012765442</v>
       </c>
       <c r="K19" t="n">
-        <v>2.032668102478756</v>
+        <v>2.012852221874569</v>
       </c>
       <c r="L19" t="n">
-        <v>11.39003410551051</v>
+        <v>11.39282741155926</v>
       </c>
       <c r="M19" t="n">
-        <v>2.978725246373724</v>
+        <v>2.932355931551956</v>
       </c>
       <c r="N19" t="n">
-        <v>0.5377833642992098</v>
+        <v>0.5120134711810558</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1091862212118263</v>
+        <v>0.1006634687822661</v>
       </c>
       <c r="P19" t="n">
-        <v>6.795611432910858</v>
+        <v>7.065385808263474</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.9135015440495705</v>
+        <v>1.024059879551301</v>
       </c>
       <c r="R19" t="n">
-        <v>9.921059862515415</v>
+        <v>10.21721804683181</v>
       </c>
       <c r="S19" t="n">
-        <v>2.071290892780488</v>
+        <v>2.084793641690672</v>
       </c>
       <c r="T19" t="n">
-        <v>0.4328042284986798</v>
+        <v>0.4335499898427331</v>
       </c>
       <c r="U19" t="inlineStr">
         <is>
@@ -5295,7 +5299,7 @@
         </is>
       </c>
       <c r="W19" t="n">
-        <v>0.4860327627622528</v>
+        <v>0.4844628548595775</v>
       </c>
     </row>
     <row r="20">
@@ -5305,61 +5309,61 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.9861889486491532</v>
+        <v>0.9689284928995144</v>
       </c>
       <c r="C20" t="n">
-        <v>0.002994649469263929</v>
+        <v>0.005619958124154002</v>
       </c>
       <c r="D20" t="n">
-        <v>1.244789285098475</v>
+        <v>1.911089175164303</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1157471414480904</v>
+        <v>0.130982818423608</v>
       </c>
       <c r="F20" t="n">
-        <v>1.767665565080966</v>
+        <v>2.656538688293582</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1696089792019564</v>
+        <v>0.1995740233801007</v>
       </c>
       <c r="H20" t="n">
-        <v>0.6345179902399187</v>
+        <v>0.6307480305053531</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1305705194017912</v>
+        <v>0.1320271866743593</v>
       </c>
       <c r="J20" t="n">
-        <v>5.830936656177133</v>
+        <v>5.956100188179828</v>
       </c>
       <c r="K20" t="n">
-        <v>0.7636096498689617</v>
+        <v>0.7656459309580322</v>
       </c>
       <c r="L20" t="n">
-        <v>8.306519763690881</v>
+        <v>8.350820114750128</v>
       </c>
       <c r="M20" t="n">
-        <v>1.404014371751256</v>
+        <v>1.42461334111197</v>
       </c>
       <c r="N20" t="n">
-        <v>0.6526113161425383</v>
+        <v>0.6418195140439492</v>
       </c>
       <c r="O20" t="n">
-        <v>0.09810257551495513</v>
+        <v>0.09590352008770091</v>
       </c>
       <c r="P20" t="n">
-        <v>6.001896242317494</v>
+        <v>6.145932765222365</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.6562287364198732</v>
+        <v>0.6359293837803782</v>
       </c>
       <c r="R20" t="n">
-        <v>8.56084533751352</v>
+        <v>8.702305897978762</v>
       </c>
       <c r="S20" t="n">
-        <v>1.15647221472566</v>
+        <v>1.11367870148036</v>
       </c>
       <c r="T20" t="n">
-        <v>0.3335776325066149</v>
+        <v>0.3271089788555652</v>
       </c>
       <c r="U20" t="inlineStr">
         <is>
@@ -5372,7 +5376,7 @@
         </is>
       </c>
       <c r="W20" t="n">
-        <v>0.5049815979134623</v>
+        <v>0.4486761973600507</v>
       </c>
     </row>
     <row r="21">
@@ -5382,61 +5386,61 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.9871179195111625</v>
+        <v>0.9692005410221173</v>
       </c>
       <c r="C21" t="n">
-        <v>0.002359068158468191</v>
+        <v>0.006212534125556454</v>
       </c>
       <c r="D21" t="n">
-        <v>1.169967310286348</v>
+        <v>1.84106996046136</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1634976126932077</v>
+        <v>0.2333842008977969</v>
       </c>
       <c r="F21" t="n">
-        <v>1.642502606376544</v>
+        <v>2.535575827527034</v>
       </c>
       <c r="G21" t="n">
-        <v>0.2010480749282015</v>
+        <v>0.2950102077098801</v>
       </c>
       <c r="H21" t="n">
-        <v>0.5049815979134623</v>
+        <v>0.422902621141039</v>
       </c>
       <c r="I21" t="n">
-        <v>0.07576486186526878</v>
+        <v>0.1406711332008928</v>
       </c>
       <c r="J21" t="n">
-        <v>7.923917410125403</v>
+        <v>8.605448924157439</v>
       </c>
       <c r="K21" t="n">
-        <v>1.936217529553563</v>
+        <v>1.766215765966688</v>
       </c>
       <c r="L21" t="n">
-        <v>10.97981639024868</v>
+        <v>11.71197174282898</v>
       </c>
       <c r="M21" t="n">
-        <v>2.312190399651964</v>
+        <v>2.286752206087009</v>
       </c>
       <c r="N21" t="n">
-        <v>0.4544702399216466</v>
+        <v>0.4281417063439478</v>
       </c>
       <c r="O21" t="n">
-        <v>0.1345335989989198</v>
+        <v>0.09729795235118779</v>
       </c>
       <c r="P21" t="n">
-        <v>7.543808145564974</v>
+        <v>7.827752113930683</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.286174227873372</v>
+        <v>0.9390066673454479</v>
       </c>
       <c r="R21" t="n">
-        <v>10.79578526937301</v>
+        <v>11.01082854408628</v>
       </c>
       <c r="S21" t="n">
-        <v>2.332243837764302</v>
+        <v>1.718763518611727</v>
       </c>
       <c r="T21" t="n">
-        <v>0.5326476795895159</v>
+        <v>0.5410588346781695</v>
       </c>
       <c r="U21" t="inlineStr">
         <is>
@@ -5449,7 +5453,7 @@
         </is>
       </c>
       <c r="W21" t="n">
-        <v>0.5049815979134623</v>
+        <v>0.4486761973600507</v>
       </c>
     </row>
     <row r="22">
@@ -5609,69 +5613,69 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Ridge</t>
+          <t>MLP</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.3017274813839386</v>
+        <v>0.9753411197979568</v>
       </c>
       <c r="C24" t="n">
-        <v>0.04245845829853616</v>
+        <v>0.01115192506325255</v>
       </c>
       <c r="D24" t="n">
-        <v>9.581932933990144</v>
+        <v>1.550996690678982</v>
       </c>
       <c r="E24" t="n">
-        <v>0.3857167518776466</v>
+        <v>0.321683428716965</v>
       </c>
       <c r="F24" t="n">
-        <v>12.65678892477901</v>
+        <v>2.314352309126113</v>
       </c>
       <c r="G24" t="n">
-        <v>0.4782124568694582</v>
+        <v>0.4940823584909748</v>
       </c>
       <c r="H24" t="n">
-        <v>-5.354942531076233e+18</v>
+        <v>0.5134801859276779</v>
       </c>
       <c r="I24" t="n">
-        <v>2.620745654277621e+19</v>
+        <v>0.1531943028549214</v>
       </c>
       <c r="J24" t="n">
-        <v>886294564.5101218</v>
+        <v>6.633856325823493</v>
       </c>
       <c r="K24" t="n">
-        <v>4218840269.421201</v>
+        <v>0.709623132161472</v>
       </c>
       <c r="L24" t="n">
-        <v>6634047895.193895</v>
+        <v>9.585029235689177</v>
       </c>
       <c r="M24" t="n">
-        <v>31570804712.53345</v>
+        <v>1.194204687850827</v>
       </c>
       <c r="N24" t="n">
-        <v>-2.614720185200482e+18</v>
+        <v>0.511053070156766</v>
       </c>
       <c r="O24" t="n">
-        <v>1.110300811727718e+19</v>
+        <v>0.2024638566875647</v>
       </c>
       <c r="P24" t="n">
-        <v>751653461.5551529</v>
+        <v>6.794052525644784</v>
       </c>
       <c r="Q24" t="n">
-        <v>2179476315.131393</v>
+        <v>0.9157127415956129</v>
       </c>
       <c r="R24" t="n">
-        <v>6301916087.371247</v>
+        <v>9.991038029243583</v>
       </c>
       <c r="S24" t="n">
-        <v>18247606035.09768</v>
+        <v>1.645179966831313</v>
       </c>
       <c r="T24" t="n">
-        <v>2.614720185200482e+18</v>
+        <v>0.4642880496411907</v>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>engineered_9</t>
+          <t>engineered_12</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
@@ -5680,75 +5684,75 @@
         </is>
       </c>
       <c r="W24" t="n">
-        <v>-6.67573790523749e+18</v>
+        <v>0.3698460606321731</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Ridge</t>
+          <t>MLP</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.3028666120136593</v>
+        <v>0.9821531677069449</v>
       </c>
       <c r="C25" t="n">
-        <v>0.03202546233915261</v>
+        <v>0.002015942007211611</v>
       </c>
       <c r="D25" t="n">
-        <v>9.215621759269562</v>
+        <v>1.364461224048362</v>
       </c>
       <c r="E25" t="n">
-        <v>0.5061534116841634</v>
+        <v>0.01879894310199522</v>
       </c>
       <c r="F25" t="n">
-        <v>12.12042029791032</v>
+        <v>1.931767267286485</v>
       </c>
       <c r="G25" t="n">
-        <v>0.7277906443328634</v>
+        <v>0.07093042884423895</v>
       </c>
       <c r="H25" t="n">
-        <v>-6.67573790523749e+18</v>
+        <v>0.3368738840332105</v>
       </c>
       <c r="I25" t="n">
-        <v>1.136174108818858e+19</v>
+        <v>0.2709023758495344</v>
       </c>
       <c r="J25" t="n">
-        <v>3198397815.310421</v>
+        <v>8.840861749816899</v>
       </c>
       <c r="K25" t="n">
-        <v>4814635434.086393</v>
+        <v>1.522972296533523</v>
       </c>
       <c r="L25" t="n">
-        <v>24281027362.19344</v>
+        <v>12.30827682493659</v>
       </c>
       <c r="M25" t="n">
-        <v>36964251862.17149</v>
+        <v>2.160831217956384</v>
       </c>
       <c r="N25" t="n">
-        <v>-3.836720691720109e+19</v>
+        <v>0.3355019483982192</v>
       </c>
       <c r="O25" t="n">
-        <v>7.673441383440219e+19</v>
+        <v>0.4297125477812171</v>
       </c>
       <c r="P25" t="n">
-        <v>3889312002.333728</v>
+        <v>7.891299962993109</v>
       </c>
       <c r="Q25" t="n">
-        <v>7778623983.68754</v>
+        <v>1.496440678066479</v>
       </c>
       <c r="R25" t="n">
-        <v>32771925373.87728</v>
+        <v>11.16028015812556</v>
       </c>
       <c r="S25" t="n">
-        <v>65543850720.03731</v>
+        <v>2.314954475443903</v>
       </c>
       <c r="T25" t="n">
-        <v>3.836720691720109e+19</v>
+        <v>0.6466512193087257</v>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>engineered_9</t>
+          <t>engineered_12</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
@@ -5757,71 +5761,71 @@
         </is>
       </c>
       <c r="W25" t="n">
-        <v>-6.67573790523749e+18</v>
+        <v>0.3698460606321731</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Lasso</t>
+          <t>Ridge</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.3145077646979687</v>
+        <v>0.3017274813839386</v>
       </c>
       <c r="C26" t="n">
-        <v>0.04681146776188484</v>
+        <v>0.04245845829853616</v>
       </c>
       <c r="D26" t="n">
-        <v>9.544782796920195</v>
+        <v>9.581932933990144</v>
       </c>
       <c r="E26" t="n">
-        <v>0.3955672554265665</v>
+        <v>0.3857167518776466</v>
       </c>
       <c r="F26" t="n">
-        <v>12.53776543223814</v>
+        <v>12.65678892477901</v>
       </c>
       <c r="G26" t="n">
-        <v>0.4860381725060588</v>
+        <v>0.4782124568694582</v>
       </c>
       <c r="H26" t="n">
-        <v>-1.052984222468353e+19</v>
+        <v>-5.354942531076233e+18</v>
       </c>
       <c r="I26" t="n">
-        <v>5.158548104497501e+19</v>
+        <v>2.620745654277621e+19</v>
       </c>
       <c r="J26" t="n">
-        <v>1209119005.648464</v>
+        <v>886294564.5101218</v>
       </c>
       <c r="K26" t="n">
-        <v>5923449157.103641</v>
+        <v>4218840269.421201</v>
       </c>
       <c r="L26" t="n">
-        <v>9048218057.625589</v>
+        <v>6634047895.193895</v>
       </c>
       <c r="M26" t="n">
-        <v>44327034584.31734</v>
+        <v>31570804712.53345</v>
       </c>
       <c r="N26" t="n">
-        <v>-6.073941624248813e+16</v>
+        <v>-2.614720185200482e+18</v>
       </c>
       <c r="O26" t="n">
-        <v>2.975611541372253e+17</v>
+        <v>1.110300811727718e+19</v>
       </c>
       <c r="P26" t="n">
-        <v>86419437.33693585</v>
+        <v>751653461.5551529</v>
       </c>
       <c r="Q26" t="n">
-        <v>423367002.0249569</v>
+        <v>2179476315.131393</v>
       </c>
       <c r="R26" t="n">
-        <v>728183050.7430501</v>
+        <v>6301916087.371247</v>
       </c>
       <c r="S26" t="n">
-        <v>3567353763.575058</v>
+        <v>18247606035.09768</v>
       </c>
       <c r="T26" t="n">
-        <v>6.073941624248813e+16</v>
+        <v>2.614720185200482e+18</v>
       </c>
       <c r="U26" t="inlineStr">
         <is>
@@ -5834,71 +5838,71 @@
         </is>
       </c>
       <c r="W26" t="n">
-        <v>0.0974414990817339</v>
+        <v>-6.67573790523749e+18</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Lasso</t>
+          <t>Ridge</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.3171606128034209</v>
+        <v>0.3028666120136593</v>
       </c>
       <c r="C27" t="n">
-        <v>0.03414686844680487</v>
+        <v>0.03202546233915261</v>
       </c>
       <c r="D27" t="n">
-        <v>9.167500766550065</v>
+        <v>9.215621759269562</v>
       </c>
       <c r="E27" t="n">
-        <v>0.5122938875838751</v>
+        <v>0.5061534116841634</v>
       </c>
       <c r="F27" t="n">
-        <v>11.99364777333075</v>
+        <v>12.12042029791032</v>
       </c>
       <c r="G27" t="n">
-        <v>0.7069472604612436</v>
+        <v>0.7277906443328634</v>
       </c>
       <c r="H27" t="n">
-        <v>0.0974414990817339</v>
+        <v>-6.67573790523749e+18</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1220281153981954</v>
+        <v>1.136174108818858e+19</v>
       </c>
       <c r="J27" t="n">
-        <v>11.41160935626219</v>
+        <v>3198397815.310421</v>
       </c>
       <c r="K27" t="n">
-        <v>1.644256263492955</v>
+        <v>4814635434.086393</v>
       </c>
       <c r="L27" t="n">
-        <v>14.80293125139776</v>
+        <v>24281027362.19344</v>
       </c>
       <c r="M27" t="n">
-        <v>2.917698424897909</v>
+        <v>36964251862.17149</v>
       </c>
       <c r="N27" t="n">
-        <v>-4.28992119453054e+19</v>
+        <v>-3.836720691720109e+19</v>
       </c>
       <c r="O27" t="n">
-        <v>8.57984238906108e+19</v>
+        <v>7.673441383440219e+19</v>
       </c>
       <c r="P27" t="n">
-        <v>4112608310.724288</v>
+        <v>3889312002.333728</v>
       </c>
       <c r="Q27" t="n">
-        <v>8225216600.368011</v>
+        <v>7778623983.68754</v>
       </c>
       <c r="R27" t="n">
-        <v>34653453511.83074</v>
+        <v>32771925373.87728</v>
       </c>
       <c r="S27" t="n">
-        <v>69306906995.8976</v>
+        <v>65543850720.03731</v>
       </c>
       <c r="T27" t="n">
-        <v>4.28992119453054e+19</v>
+        <v>3.836720691720109e+19</v>
       </c>
       <c r="U27" t="inlineStr">
         <is>
@@ -5911,71 +5915,71 @@
         </is>
       </c>
       <c r="W27" t="n">
-        <v>0.0974414990817339</v>
+        <v>-6.67573790523749e+18</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ElasticNet</t>
+          <t>Lasso</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.2915120633993095</v>
+        <v>0.3145077646979687</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0451097797698668</v>
+        <v>0.04681146776188484</v>
       </c>
       <c r="D28" t="n">
-        <v>9.656422356101782</v>
+        <v>9.544782796920195</v>
       </c>
       <c r="E28" t="n">
-        <v>0.3819785900553825</v>
+        <v>0.3955672554265665</v>
       </c>
       <c r="F28" t="n">
-        <v>12.7474505965697</v>
+        <v>12.53776543223814</v>
       </c>
       <c r="G28" t="n">
-        <v>0.4716163724628968</v>
+        <v>0.4860381725060588</v>
       </c>
       <c r="H28" t="n">
-        <v>-5.861047574352072e+17</v>
+        <v>-1.052984222468353e+19</v>
       </c>
       <c r="I28" t="n">
-        <v>2.871315183067926e+18</v>
+        <v>5.158548104497501e+19</v>
       </c>
       <c r="J28" t="n">
-        <v>285263200.3572531</v>
+        <v>1209119005.648464</v>
       </c>
       <c r="K28" t="n">
-        <v>1397498519.460929</v>
+        <v>5923449157.103641</v>
       </c>
       <c r="L28" t="n">
-        <v>2134714261.550833</v>
+        <v>9048218057.625589</v>
       </c>
       <c r="M28" t="n">
-        <v>10457921313.71948</v>
+        <v>44327034584.31734</v>
       </c>
       <c r="N28" t="n">
-        <v>0.1981406883508078</v>
+        <v>-6.073941624248813e+16</v>
       </c>
       <c r="O28" t="n">
-        <v>0.1261399745055366</v>
+        <v>2.975611541372253e+17</v>
       </c>
       <c r="P28" t="n">
-        <v>9.984406786729414</v>
+        <v>86419437.33693585</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.096875142180235</v>
+        <v>423367002.0249569</v>
       </c>
       <c r="R28" t="n">
-        <v>13.13888327051949</v>
+        <v>728183050.7430501</v>
       </c>
       <c r="S28" t="n">
-        <v>1.495461510166714</v>
+        <v>3567353763.575058</v>
       </c>
       <c r="T28" t="n">
-        <v>0.09337137504850168</v>
+        <v>6.073941624248813e+16</v>
       </c>
       <c r="U28" t="inlineStr">
         <is>
@@ -5988,71 +5992,71 @@
         </is>
       </c>
       <c r="W28" t="n">
-        <v>0.09671526165271145</v>
+        <v>0.0974414990817339</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ElasticNet</t>
+          <t>Lasso</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.2900397654416775</v>
+        <v>0.3171606128034209</v>
       </c>
       <c r="C29" t="n">
-        <v>0.03339473256054176</v>
+        <v>0.03414686844680487</v>
       </c>
       <c r="D29" t="n">
-        <v>9.307152179964035</v>
+        <v>9.167500766550065</v>
       </c>
       <c r="E29" t="n">
-        <v>0.4970938880874273</v>
+        <v>0.5122938875838751</v>
       </c>
       <c r="F29" t="n">
-        <v>12.22921418501236</v>
+        <v>11.99364777333075</v>
       </c>
       <c r="G29" t="n">
-        <v>0.7010558303701281</v>
+        <v>0.7069472604612436</v>
       </c>
       <c r="H29" t="n">
-        <v>0.09671526165271145</v>
+        <v>0.0974414990817339</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1054683400461065</v>
+        <v>0.1220281153981954</v>
       </c>
       <c r="J29" t="n">
-        <v>11.39200955929109</v>
+        <v>11.41160935626219</v>
       </c>
       <c r="K29" t="n">
-        <v>1.824829210680723</v>
+        <v>1.644256263492955</v>
       </c>
       <c r="L29" t="n">
-        <v>14.85781438869295</v>
+        <v>14.80293125139776</v>
       </c>
       <c r="M29" t="n">
-        <v>3.094254723700803</v>
+        <v>2.917698424897909</v>
       </c>
       <c r="N29" t="n">
-        <v>-1.312899313230605e+19</v>
+        <v>-4.28992119453054e+19</v>
       </c>
       <c r="O29" t="n">
-        <v>2.62579862646121e+19</v>
+        <v>8.57984238906108e+19</v>
       </c>
       <c r="P29" t="n">
-        <v>2275141451.654634</v>
+        <v>4112608310.724288</v>
       </c>
       <c r="Q29" t="n">
-        <v>4550282882.09878</v>
+        <v>8225216600.368011</v>
       </c>
       <c r="R29" t="n">
-        <v>19170682553.48537</v>
+        <v>34653453511.83074</v>
       </c>
       <c r="S29" t="n">
-        <v>38341365078.95857</v>
+        <v>69306906995.8976</v>
       </c>
       <c r="T29" t="n">
-        <v>1.312899313230605e+19</v>
+        <v>4.28992119453054e+19</v>
       </c>
       <c r="U29" t="inlineStr">
         <is>
@@ -6065,71 +6069,71 @@
         </is>
       </c>
       <c r="W29" t="n">
-        <v>0.09671526165271145</v>
+        <v>0.0974414990817339</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Ridge+Poly</t>
+          <t>ElasticNet</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.552041625399313</v>
+        <v>0.2915120633993095</v>
       </c>
       <c r="C30" t="n">
-        <v>0.05406565633694228</v>
+        <v>0.0451097797698668</v>
       </c>
       <c r="D30" t="n">
-        <v>7.6762911899414</v>
+        <v>9.656422356101782</v>
       </c>
       <c r="E30" t="n">
-        <v>0.3891427533313494</v>
+        <v>0.3819785900553825</v>
       </c>
       <c r="F30" t="n">
-        <v>10.11590366200946</v>
+        <v>12.7474505965697</v>
       </c>
       <c r="G30" t="n">
-        <v>0.5721053925467848</v>
+        <v>0.4716163724628968</v>
       </c>
       <c r="H30" t="n">
-        <v>-7.520177329183921e+19</v>
+        <v>-5.861047574352072e+17</v>
       </c>
       <c r="I30" t="n">
-        <v>3.011458704894959e+20</v>
+        <v>2.871315183067926e+18</v>
       </c>
       <c r="J30" t="n">
-        <v>4209203915.208248</v>
+        <v>285263200.3572531</v>
       </c>
       <c r="K30" t="n">
-        <v>15322305601.89563</v>
+        <v>1397498519.460929</v>
       </c>
       <c r="L30" t="n">
-        <v>31586398159.22511</v>
+        <v>2134714261.550833</v>
       </c>
       <c r="M30" t="n">
-        <v>114826480893.1301</v>
+        <v>10457921313.71948</v>
       </c>
       <c r="N30" t="n">
-        <v>-3.560642177403972e+19</v>
+        <v>0.1981406883508078</v>
       </c>
       <c r="O30" t="n">
-        <v>1.027547524653516e+20</v>
+        <v>0.1261399745055366</v>
       </c>
       <c r="P30" t="n">
-        <v>3665630247.656944</v>
+        <v>9.984406786729414</v>
       </c>
       <c r="Q30" t="n">
-        <v>8219533794.28051</v>
+        <v>1.096875142180235</v>
       </c>
       <c r="R30" t="n">
-        <v>30750928571.37959</v>
+        <v>13.13888327051949</v>
       </c>
       <c r="S30" t="n">
-        <v>68909727896.76645</v>
+        <v>1.495461510166714</v>
       </c>
       <c r="T30" t="n">
-        <v>3.560642177403972e+19</v>
+        <v>0.09337137504850168</v>
       </c>
       <c r="U30" t="inlineStr">
         <is>
@@ -6142,71 +6146,71 @@
         </is>
       </c>
       <c r="W30" t="n">
-        <v>-1.072922916415649e+20</v>
+        <v>0.09671526165271145</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Ridge+Poly</t>
+          <t>ElasticNet</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.5723953700531301</v>
+        <v>0.2900397654416775</v>
       </c>
       <c r="C31" t="n">
-        <v>0.0400671352521368</v>
+        <v>0.03339473256054176</v>
       </c>
       <c r="D31" t="n">
-        <v>7.18974384821215</v>
+        <v>9.307152179964035</v>
       </c>
       <c r="E31" t="n">
-        <v>0.3970198890048484</v>
+        <v>0.4970938880874273</v>
       </c>
       <c r="F31" t="n">
-        <v>9.472186216950249</v>
+        <v>12.22921418501236</v>
       </c>
       <c r="G31" t="n">
-        <v>0.4932211243401074</v>
+        <v>0.7010558303701281</v>
       </c>
       <c r="H31" t="n">
-        <v>-1.072922916415649e+20</v>
+        <v>0.09671526165271145</v>
       </c>
       <c r="I31" t="n">
-        <v>1.691308404056939e+20</v>
+        <v>0.1054683400461065</v>
       </c>
       <c r="J31" t="n">
-        <v>11863821208.42979</v>
+        <v>11.39200955929109</v>
       </c>
       <c r="K31" t="n">
-        <v>15130434754.74315</v>
+        <v>1.824829210680723</v>
       </c>
       <c r="L31" t="n">
-        <v>88213712057.66719</v>
+        <v>14.85781438869295</v>
       </c>
       <c r="M31" t="n">
-        <v>111559520484.0263</v>
+        <v>3.094254723700803</v>
       </c>
       <c r="N31" t="n">
-        <v>-9.844493573592266e+16</v>
+        <v>-1.312899313230605e+19</v>
       </c>
       <c r="O31" t="n">
-        <v>1.968898714718453e+17</v>
+        <v>2.62579862646121e+19</v>
       </c>
       <c r="P31" t="n">
-        <v>197010511.8823705</v>
+        <v>2275141451.654634</v>
       </c>
       <c r="Q31" t="n">
-        <v>394021005.6061086</v>
+        <v>4550282882.09878</v>
       </c>
       <c r="R31" t="n">
-        <v>1660040017.234343</v>
+        <v>19170682553.48537</v>
       </c>
       <c r="S31" t="n">
-        <v>3320080010.681612</v>
+        <v>38341365078.95857</v>
       </c>
       <c r="T31" t="n">
-        <v>9.844493573592266e+16</v>
+        <v>1.312899313230605e+19</v>
       </c>
       <c r="U31" t="inlineStr">
         <is>
@@ -6219,71 +6223,71 @@
         </is>
       </c>
       <c r="W31" t="n">
-        <v>-1.072922916415649e+20</v>
+        <v>0.09671526165271145</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>BayesianRidge</t>
+          <t>Ridge+Poly</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.3325656908440721</v>
+        <v>0.552041625399313</v>
       </c>
       <c r="C32" t="n">
-        <v>0.04674057700069163</v>
+        <v>0.05406565633694228</v>
       </c>
       <c r="D32" t="n">
-        <v>9.396774192987232</v>
+        <v>7.6762911899414</v>
       </c>
       <c r="E32" t="n">
-        <v>0.3860024690584094</v>
+        <v>0.3891427533313494</v>
       </c>
       <c r="F32" t="n">
-        <v>12.37157766596251</v>
+        <v>10.11590366200946</v>
       </c>
       <c r="G32" t="n">
-        <v>0.4996143617740376</v>
+        <v>0.5721053925467848</v>
       </c>
       <c r="H32" t="n">
-        <v>-4.143170524023389e+19</v>
+        <v>-7.520177329183921e+19</v>
       </c>
       <c r="I32" t="n">
-        <v>1.909383219572614e+20</v>
+        <v>3.011458704894959e+20</v>
       </c>
       <c r="J32" t="n">
-        <v>2858031114.755757</v>
+        <v>4209203915.208248</v>
       </c>
       <c r="K32" t="n">
-        <v>11586786434.98934</v>
+        <v>15322305601.89563</v>
       </c>
       <c r="L32" t="n">
-        <v>21422871238.75453</v>
+        <v>31586398159.22511</v>
       </c>
       <c r="M32" t="n">
-        <v>86739498629.32147</v>
+        <v>114826480893.1301</v>
       </c>
       <c r="N32" t="n">
-        <v>-1.301642117577251e+19</v>
+        <v>-3.560642177403972e+19</v>
       </c>
       <c r="O32" t="n">
-        <v>3.503842444441881e+19</v>
+        <v>1.027547524653516e+20</v>
       </c>
       <c r="P32" t="n">
-        <v>2311673849.236787</v>
+        <v>3665630247.656944</v>
       </c>
       <c r="Q32" t="n">
-        <v>5149138959.075474</v>
+        <v>8219533794.28051</v>
       </c>
       <c r="R32" t="n">
-        <v>19396677631.59528</v>
+        <v>30750928571.37959</v>
       </c>
       <c r="S32" t="n">
-        <v>43220010437.22935</v>
+        <v>68909727896.76645</v>
       </c>
       <c r="T32" t="n">
-        <v>1.301642117577251e+19</v>
+        <v>3.560642177403972e+19</v>
       </c>
       <c r="U32" t="inlineStr">
         <is>
@@ -6296,71 +6300,71 @@
         </is>
       </c>
       <c r="W32" t="n">
-        <v>-2.971698601396009e+19</v>
+        <v>-1.072922916415649e+20</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>BayesianRidge</t>
+          <t>Ridge+Poly</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.3371445890258222</v>
+        <v>0.5723953700531301</v>
       </c>
       <c r="C33" t="n">
-        <v>0.0354102971649844</v>
+        <v>0.0400671352521368</v>
       </c>
       <c r="D33" t="n">
-        <v>9.026588032441868</v>
+        <v>7.18974384821215</v>
       </c>
       <c r="E33" t="n">
-        <v>0.5153807364698074</v>
+        <v>0.3970198890048484</v>
       </c>
       <c r="F33" t="n">
-        <v>11.81812977443367</v>
+        <v>9.472186216950249</v>
       </c>
       <c r="G33" t="n">
-        <v>0.7343945197562571</v>
+        <v>0.4932211243401074</v>
       </c>
       <c r="H33" t="n">
-        <v>-2.971698601396009e+19</v>
+        <v>-1.072922916415649e+20</v>
       </c>
       <c r="I33" t="n">
-        <v>5.915361205257721e+19</v>
+        <v>1.691308404056939e+20</v>
       </c>
       <c r="J33" t="n">
-        <v>4575700782.638616</v>
+        <v>11863821208.42979</v>
       </c>
       <c r="K33" t="n">
-        <v>8316397255.681125</v>
+        <v>15130434754.74315</v>
       </c>
       <c r="L33" t="n">
-        <v>33449856234.15522</v>
+        <v>88213712057.66719</v>
       </c>
       <c r="M33" t="n">
-        <v>60497487274.48281</v>
+        <v>111559520484.0263</v>
       </c>
       <c r="N33" t="n">
-        <v>-1.025208226003857e+20</v>
+        <v>-9.844493573592266e+16</v>
       </c>
       <c r="O33" t="n">
-        <v>2.050416452007713e+20</v>
+        <v>1.968898714718453e+17</v>
       </c>
       <c r="P33" t="n">
-        <v>6357680988.188044</v>
+        <v>197010511.8823705</v>
       </c>
       <c r="Q33" t="n">
-        <v>12715361955.52387</v>
+        <v>394021005.6061086</v>
       </c>
       <c r="R33" t="n">
-        <v>53570772144.8055</v>
+        <v>1660040017.234343</v>
       </c>
       <c r="S33" t="n">
-        <v>107141544262.1257</v>
+        <v>3320080010.681612</v>
       </c>
       <c r="T33" t="n">
-        <v>1.025208226003857e+20</v>
+        <v>9.844493573592266e+16</v>
       </c>
       <c r="U33" t="inlineStr">
         <is>
@@ -6373,71 +6377,71 @@
         </is>
       </c>
       <c r="W33" t="n">
-        <v>-2.971698601396009e+19</v>
+        <v>-1.072922916415649e+20</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>GaussianProcess</t>
+          <t>BayesianRidge</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.9065966657166006</v>
+        <v>0.3325656908440721</v>
       </c>
       <c r="C34" t="n">
-        <v>0.03085323860497451</v>
+        <v>0.04674057700069163</v>
       </c>
       <c r="D34" t="n">
-        <v>3.117551636425061</v>
+        <v>9.396774192987232</v>
       </c>
       <c r="E34" t="n">
-        <v>0.5186726380414457</v>
+        <v>0.3860024690584094</v>
       </c>
       <c r="F34" t="n">
-        <v>4.56383275644751</v>
+        <v>12.37157766596251</v>
       </c>
       <c r="G34" t="n">
-        <v>0.729609700561953</v>
+        <v>0.4996143617740376</v>
       </c>
       <c r="H34" t="n">
-        <v>0.5965366426204011</v>
+        <v>-4.143170524023389e+19</v>
       </c>
       <c r="I34" t="n">
-        <v>0.1025593938225101</v>
+        <v>1.909383219572614e+20</v>
       </c>
       <c r="J34" t="n">
-        <v>6.283191510609035</v>
+        <v>2858031114.755757</v>
       </c>
       <c r="K34" t="n">
-        <v>0.6912027807352193</v>
+        <v>11586786434.98934</v>
       </c>
       <c r="L34" t="n">
-        <v>8.822286901642284</v>
+        <v>21422871238.75453</v>
       </c>
       <c r="M34" t="n">
-        <v>1.209868565230645</v>
+        <v>86739498629.32147</v>
       </c>
       <c r="N34" t="n">
-        <v>0.6318264138040046</v>
+        <v>-1.301642117577251e+19</v>
       </c>
       <c r="O34" t="n">
-        <v>0.09399642525252064</v>
+        <v>3.503842444441881e+19</v>
       </c>
       <c r="P34" t="n">
-        <v>6.29790045406229</v>
+        <v>2311673849.236787</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.7680714742265431</v>
+        <v>5149138959.075474</v>
       </c>
       <c r="R34" t="n">
-        <v>8.846115289558574</v>
+        <v>19396677631.59528</v>
       </c>
       <c r="S34" t="n">
-        <v>1.351681855421077</v>
+        <v>43220010437.22935</v>
       </c>
       <c r="T34" t="n">
-        <v>0.274770251912596</v>
+        <v>1.301642117577251e+19</v>
       </c>
       <c r="U34" t="inlineStr">
         <is>
@@ -6450,71 +6454,71 @@
         </is>
       </c>
       <c r="W34" t="n">
-        <v>0.338739223385862</v>
+        <v>-2.971698601396009e+19</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>GaussianProcess</t>
+          <t>BayesianRidge</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.9387964054919982</v>
+        <v>0.3371445890258222</v>
       </c>
       <c r="C35" t="n">
-        <v>0.008677130884169087</v>
+        <v>0.0354102971649844</v>
       </c>
       <c r="D35" t="n">
-        <v>2.395266906608295</v>
+        <v>9.026588032441868</v>
       </c>
       <c r="E35" t="n">
-        <v>0.1217953016369874</v>
+        <v>0.5153807364698074</v>
       </c>
       <c r="F35" t="n">
-        <v>3.574333215734995</v>
+        <v>11.81812977443367</v>
       </c>
       <c r="G35" t="n">
-        <v>0.2149291260472835</v>
+        <v>0.7343945197562571</v>
       </c>
       <c r="H35" t="n">
-        <v>0.338739223385862</v>
+        <v>-2.971698601396009e+19</v>
       </c>
       <c r="I35" t="n">
-        <v>0.08194898226787306</v>
+        <v>5.915361205257721e+19</v>
       </c>
       <c r="J35" t="n">
-        <v>9.228810889110468</v>
+        <v>4575700782.638616</v>
       </c>
       <c r="K35" t="n">
-        <v>2.037980172999492</v>
+        <v>8316397255.681125</v>
       </c>
       <c r="L35" t="n">
-        <v>12.76374934823635</v>
+        <v>33449856234.15522</v>
       </c>
       <c r="M35" t="n">
-        <v>2.945672714772734</v>
+        <v>60497487274.48281</v>
       </c>
       <c r="N35" t="n">
-        <v>0.4215082016471047</v>
+        <v>-1.025208226003857e+20</v>
       </c>
       <c r="O35" t="n">
-        <v>0.1534240783063387</v>
+        <v>2.050416452007713e+20</v>
       </c>
       <c r="P35" t="n">
-        <v>7.476780672211142</v>
+        <v>6357680988.188044</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.223812624790924</v>
+        <v>12715361955.52387</v>
       </c>
       <c r="R35" t="n">
-        <v>11.0591348434321</v>
+        <v>53570772144.8055</v>
       </c>
       <c r="S35" t="n">
-        <v>2.297127792398254</v>
+        <v>107141544262.1257</v>
       </c>
       <c r="T35" t="n">
-        <v>0.5172882038448935</v>
+        <v>1.025208226003857e+20</v>
       </c>
       <c r="U35" t="inlineStr">
         <is>
@@ -6527,71 +6531,71 @@
         </is>
       </c>
       <c r="W35" t="n">
-        <v>0.338739223385862</v>
+        <v>-2.971698601396009e+19</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SVR_RBF</t>
+          <t>GaussianProcess</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.826614154991001</v>
+        <v>0.9416135362661946</v>
       </c>
       <c r="C36" t="n">
-        <v>0.03946803088697774</v>
+        <v>0.0456964157028171</v>
       </c>
       <c r="D36" t="n">
-        <v>3.264806002505198</v>
+        <v>2.279116924335995</v>
       </c>
       <c r="E36" t="n">
-        <v>0.427532423627055</v>
+        <v>1.036201522073495</v>
       </c>
       <c r="F36" t="n">
-        <v>6.254791474187825</v>
+        <v>3.323899209442583</v>
       </c>
       <c r="G36" t="n">
-        <v>0.7152141128895573</v>
+        <v>1.49168475338137</v>
       </c>
       <c r="H36" t="n">
-        <v>0.5959124555325738</v>
+        <v>0.4334036046666883</v>
       </c>
       <c r="I36" t="n">
-        <v>0.1048310484424332</v>
+        <v>0.204793702441735</v>
       </c>
       <c r="J36" t="n">
-        <v>6.259188917785801</v>
+        <v>7.569370835388433</v>
       </c>
       <c r="K36" t="n">
-        <v>0.7001527281336271</v>
+        <v>1.895604446955941</v>
       </c>
       <c r="L36" t="n">
-        <v>8.829927446574471</v>
+        <v>10.50672095001373</v>
       </c>
       <c r="M36" t="n">
-        <v>1.164791228214837</v>
+        <v>2.538791233163131</v>
       </c>
       <c r="N36" t="n">
-        <v>0.6137629940723229</v>
+        <v>0.4398744674796945</v>
       </c>
       <c r="O36" t="n">
-        <v>0.1114196685670426</v>
+        <v>0.2751194062270017</v>
       </c>
       <c r="P36" t="n">
-        <v>6.326742738497562</v>
+        <v>7.561235677802288</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.8255305888611634</v>
+        <v>1.940706693283289</v>
       </c>
       <c r="R36" t="n">
-        <v>9.019554406652006</v>
+        <v>10.59455136730631</v>
       </c>
       <c r="S36" t="n">
-        <v>1.407882010594907</v>
+        <v>2.628333420952691</v>
       </c>
       <c r="T36" t="n">
-        <v>0.2128511609186781</v>
+        <v>0.5017390687865001</v>
       </c>
       <c r="U36" t="inlineStr">
         <is>
@@ -6604,71 +6608,71 @@
         </is>
       </c>
       <c r="W36" t="n">
-        <v>0.492357537824468</v>
+        <v>0.372970863970061</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SVR_RBF</t>
+          <t>GaussianProcess</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.8535974271150261</v>
+        <v>0.925113059289898</v>
       </c>
       <c r="C37" t="n">
-        <v>0.02457899545070582</v>
+        <v>0.02769961581694689</v>
       </c>
       <c r="D37" t="n">
-        <v>2.784504544279985</v>
+        <v>2.57565997266099</v>
       </c>
       <c r="E37" t="n">
-        <v>0.3044612937345024</v>
+        <v>0.3151247473738747</v>
       </c>
       <c r="F37" t="n">
-        <v>5.524447829251778</v>
+        <v>3.89159184114681</v>
       </c>
       <c r="G37" t="n">
-        <v>0.4646991597100477</v>
+        <v>0.5728215631278768</v>
       </c>
       <c r="H37" t="n">
-        <v>0.492357537824468</v>
+        <v>0.372970863970061</v>
       </c>
       <c r="I37" t="n">
-        <v>0.06697515857591546</v>
+        <v>0.09807592495656756</v>
       </c>
       <c r="J37" t="n">
-        <v>7.965797791312582</v>
+        <v>8.959860065700321</v>
       </c>
       <c r="K37" t="n">
-        <v>1.797000549781251</v>
+        <v>1.629031008143181</v>
       </c>
       <c r="L37" t="n">
-        <v>11.15094446230213</v>
+        <v>12.29112554889825</v>
       </c>
       <c r="M37" t="n">
-        <v>2.355502004757706</v>
+        <v>2.211812463308558</v>
       </c>
       <c r="N37" t="n">
-        <v>0.5235726680511263</v>
+        <v>0.4152400171443699</v>
       </c>
       <c r="O37" t="n">
-        <v>0.157851133375714</v>
+        <v>0.1597148620644397</v>
       </c>
       <c r="P37" t="n">
-        <v>6.912452406061801</v>
+        <v>7.587762065086193</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.960936709494852</v>
+        <v>1.214949328435606</v>
       </c>
       <c r="R37" t="n">
-        <v>9.898337464089535</v>
+        <v>11.10227884280743</v>
       </c>
       <c r="S37" t="n">
-        <v>1.773741689548711</v>
+        <v>2.279941580060175</v>
       </c>
       <c r="T37" t="n">
-        <v>0.3300247590638997</v>
+        <v>0.509873042145528</v>
       </c>
       <c r="U37" t="inlineStr">
         <is>
@@ -6681,71 +6685,71 @@
         </is>
       </c>
       <c r="W37" t="n">
-        <v>0.492357537824468</v>
+        <v>0.372970863970061</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>SVR_RBF</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.9948297211346088</v>
+        <v>0.826614154991001</v>
       </c>
       <c r="C38" t="n">
-        <v>0.001913682083040513</v>
+        <v>0.03946803088697774</v>
       </c>
       <c r="D38" t="n">
-        <v>0.2198554572271386</v>
+        <v>3.264806002505198</v>
       </c>
       <c r="E38" t="n">
-        <v>0.06729342134394246</v>
+        <v>0.427532423627055</v>
       </c>
       <c r="F38" t="n">
-        <v>1.061329360457369</v>
+        <v>6.254791474187825</v>
       </c>
       <c r="G38" t="n">
-        <v>0.2340950492271154</v>
+        <v>0.7152141128895573</v>
       </c>
       <c r="H38" t="n">
-        <v>0.544914735318256</v>
+        <v>0.5959124555325738</v>
       </c>
       <c r="I38" t="n">
-        <v>0.1160172083561237</v>
+        <v>0.1048310484424332</v>
       </c>
       <c r="J38" t="n">
-        <v>6.549146657835024</v>
+        <v>6.259188917785801</v>
       </c>
       <c r="K38" t="n">
-        <v>0.6635240895628002</v>
+        <v>0.7001527281336271</v>
       </c>
       <c r="L38" t="n">
-        <v>9.347879143102114</v>
+        <v>8.829927446574471</v>
       </c>
       <c r="M38" t="n">
-        <v>1.155422877109452</v>
+        <v>1.164791228214837</v>
       </c>
       <c r="N38" t="n">
-        <v>0.5771393196802437</v>
+        <v>0.6137629940723229</v>
       </c>
       <c r="O38" t="n">
-        <v>0.1292694753545363</v>
+        <v>0.1114196685670426</v>
       </c>
       <c r="P38" t="n">
-        <v>6.685799848894897</v>
+        <v>6.326742738497562</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.9054158385099433</v>
+        <v>0.8255305888611634</v>
       </c>
       <c r="R38" t="n">
-        <v>9.408770625019219</v>
+        <v>9.019554406652006</v>
       </c>
       <c r="S38" t="n">
-        <v>1.415976820215691</v>
+        <v>1.407882010594907</v>
       </c>
       <c r="T38" t="n">
-        <v>0.4176904014543651</v>
+        <v>0.2128511609186781</v>
       </c>
       <c r="U38" t="inlineStr">
         <is>
@@ -6758,71 +6762,71 @@
         </is>
       </c>
       <c r="W38" t="n">
-        <v>0.3719001049133902</v>
+        <v>0.492357537824468</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>SVR_RBF</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.9937553958002188</v>
+        <v>0.8535974271150261</v>
       </c>
       <c r="C39" t="n">
-        <v>0.001740433062423951</v>
+        <v>0.02457899545070582</v>
       </c>
       <c r="D39" t="n">
-        <v>0.2537150996593565</v>
+        <v>2.784504544279985</v>
       </c>
       <c r="E39" t="n">
-        <v>0.04912595877463902</v>
+        <v>0.3044612937345024</v>
       </c>
       <c r="F39" t="n">
-        <v>1.135945285284035</v>
+        <v>5.524447829251778</v>
       </c>
       <c r="G39" t="n">
-        <v>0.1600485083791818</v>
+        <v>0.4646991597100477</v>
       </c>
       <c r="H39" t="n">
-        <v>0.3719001049133902</v>
+        <v>0.492357537824468</v>
       </c>
       <c r="I39" t="n">
-        <v>0.1199008445326567</v>
+        <v>0.06697515857591546</v>
       </c>
       <c r="J39" t="n">
-        <v>8.891440378448694</v>
+        <v>7.965797791312582</v>
       </c>
       <c r="K39" t="n">
-        <v>2.046380340178274</v>
+        <v>1.797000549781251</v>
       </c>
       <c r="L39" t="n">
-        <v>12.40701933029582</v>
+        <v>11.15094446230213</v>
       </c>
       <c r="M39" t="n">
-        <v>3.016990392263865</v>
+        <v>2.355502004757706</v>
       </c>
       <c r="N39" t="n">
-        <v>0.393041828052859</v>
+        <v>0.5235726680511263</v>
       </c>
       <c r="O39" t="n">
-        <v>0.1965083729731102</v>
+        <v>0.157851133375714</v>
       </c>
       <c r="P39" t="n">
-        <v>7.849881645252809</v>
+        <v>6.912452406061801</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.772707333023437</v>
+        <v>0.960936709494852</v>
       </c>
       <c r="R39" t="n">
-        <v>11.16468926356227</v>
+        <v>9.898337464089535</v>
       </c>
       <c r="S39" t="n">
-        <v>2.013791037478235</v>
+        <v>1.773741689548711</v>
       </c>
       <c r="T39" t="n">
-        <v>0.6007135677473598</v>
+        <v>0.3300247590638997</v>
       </c>
       <c r="U39" t="inlineStr">
         <is>
@@ -6835,71 +6839,71 @@
         </is>
       </c>
       <c r="W39" t="n">
-        <v>0.3719001049133902</v>
+        <v>0.492357537824468</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ExtraTrees</t>
+          <t>KNN</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.9498620772620165</v>
+        <v>0.9948297211346088</v>
       </c>
       <c r="C40" t="n">
-        <v>0.01313765106346322</v>
+        <v>0.001913682083040513</v>
       </c>
       <c r="D40" t="n">
-        <v>2.010923314464776</v>
+        <v>0.2198554572271386</v>
       </c>
       <c r="E40" t="n">
-        <v>0.2193365919463248</v>
+        <v>0.06729342134394246</v>
       </c>
       <c r="F40" t="n">
-        <v>3.357169937931477</v>
+        <v>1.061329360457369</v>
       </c>
       <c r="G40" t="n">
-        <v>0.4354503575064478</v>
+        <v>0.2340950492271154</v>
       </c>
       <c r="H40" t="n">
-        <v>0.6721187725846244</v>
+        <v>0.544914735318256</v>
       </c>
       <c r="I40" t="n">
-        <v>0.1060085352333262</v>
+        <v>0.1160172083561237</v>
       </c>
       <c r="J40" t="n">
-        <v>5.682818651868393</v>
+        <v>6.549146657835024</v>
       </c>
       <c r="K40" t="n">
-        <v>0.6270154156238953</v>
+        <v>0.6635240895628002</v>
       </c>
       <c r="L40" t="n">
-        <v>7.915488100197918</v>
+        <v>9.347879143102114</v>
       </c>
       <c r="M40" t="n">
-        <v>1.220858428606219</v>
+        <v>1.155422877109452</v>
       </c>
       <c r="N40" t="n">
-        <v>0.6859988879406299</v>
+        <v>0.5771393196802437</v>
       </c>
       <c r="O40" t="n">
-        <v>0.1002232162553805</v>
+        <v>0.1292694753545363</v>
       </c>
       <c r="P40" t="n">
-        <v>5.742108558624855</v>
+        <v>6.685799848894897</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.7005506116739646</v>
+        <v>0.9054158385099433</v>
       </c>
       <c r="R40" t="n">
-        <v>8.115292133517002</v>
+        <v>9.408770625019219</v>
       </c>
       <c r="S40" t="n">
-        <v>1.334343894621413</v>
+        <v>1.415976820215691</v>
       </c>
       <c r="T40" t="n">
-        <v>0.2638631893213866</v>
+        <v>0.4176904014543651</v>
       </c>
       <c r="U40" t="inlineStr">
         <is>
@@ -6912,71 +6916,71 @@
         </is>
       </c>
       <c r="W40" t="n">
-        <v>0.4591833356114218</v>
+        <v>0.3719001049133902</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ExtraTrees</t>
+          <t>KNN</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.9627960212713577</v>
+        <v>0.9937553958002188</v>
       </c>
       <c r="C41" t="n">
-        <v>0.01213571363626186</v>
+        <v>0.001740433062423951</v>
       </c>
       <c r="D41" t="n">
-        <v>1.670465183879847</v>
+        <v>0.2537150996593565</v>
       </c>
       <c r="E41" t="n">
-        <v>0.2553251761809081</v>
+        <v>0.04912595877463902</v>
       </c>
       <c r="F41" t="n">
-        <v>2.760394787276929</v>
+        <v>1.135945285284035</v>
       </c>
       <c r="G41" t="n">
-        <v>0.49854917099225</v>
+        <v>0.1600485083791818</v>
       </c>
       <c r="H41" t="n">
-        <v>0.4591833356114218</v>
+        <v>0.3719001049133902</v>
       </c>
       <c r="I41" t="n">
-        <v>0.04613002346783904</v>
+        <v>0.1199008445326567</v>
       </c>
       <c r="J41" t="n">
-        <v>8.278289838762586</v>
+        <v>8.891440378448694</v>
       </c>
       <c r="K41" t="n">
-        <v>1.724709676897757</v>
+        <v>2.046380340178274</v>
       </c>
       <c r="L41" t="n">
-        <v>11.6067488546106</v>
+        <v>12.40701933029582</v>
       </c>
       <c r="M41" t="n">
-        <v>2.753705463357289</v>
+        <v>3.016990392263865</v>
       </c>
       <c r="N41" t="n">
-        <v>0.5149899516334286</v>
+        <v>0.393041828052859</v>
       </c>
       <c r="O41" t="n">
-        <v>0.1022767897758472</v>
+        <v>0.1965083729731102</v>
       </c>
       <c r="P41" t="n">
-        <v>7.033440319859958</v>
+        <v>7.849881645252809</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.091398422177912</v>
+        <v>0.772707333023437</v>
       </c>
       <c r="R41" t="n">
-        <v>10.19977221604566</v>
+        <v>11.16468926356227</v>
       </c>
       <c r="S41" t="n">
-        <v>2.161009543689747</v>
+        <v>2.013791037478235</v>
       </c>
       <c r="T41" t="n">
-        <v>0.447806069637929</v>
+        <v>0.6007135677473598</v>
       </c>
       <c r="U41" t="inlineStr">
         <is>
@@ -6989,71 +6993,71 @@
         </is>
       </c>
       <c r="W41" t="n">
-        <v>0.4591833356114218</v>
+        <v>0.3719001049133902</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>HistGradientBoosting</t>
+          <t>ExtraTrees</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.9403087098851554</v>
+        <v>0.957241867839988</v>
       </c>
       <c r="C42" t="n">
-        <v>0.009508631994000755</v>
+        <v>0.0127650822379566</v>
       </c>
       <c r="D42" t="n">
-        <v>2.65098770004651</v>
+        <v>1.822026732386619</v>
       </c>
       <c r="E42" t="n">
-        <v>0.1732408869301957</v>
+        <v>0.2340762234497593</v>
       </c>
       <c r="F42" t="n">
-        <v>3.684840031955568</v>
+        <v>3.093762227103618</v>
       </c>
       <c r="G42" t="n">
-        <v>0.2581380811135006</v>
+        <v>0.4605067077390598</v>
       </c>
       <c r="H42" t="n">
-        <v>0.5902063618623242</v>
+        <v>0.6714183085920803</v>
       </c>
       <c r="I42" t="n">
-        <v>0.1258297540943074</v>
+        <v>0.1094796054135673</v>
       </c>
       <c r="J42" t="n">
-        <v>6.372475939126946</v>
+        <v>5.635511568882954</v>
       </c>
       <c r="K42" t="n">
-        <v>0.6747467681931221</v>
+        <v>0.6485217276002692</v>
       </c>
       <c r="L42" t="n">
-        <v>8.820669534902047</v>
+        <v>7.913907115251006</v>
       </c>
       <c r="M42" t="n">
-        <v>1.236544656635436</v>
+        <v>1.251929339226198</v>
       </c>
       <c r="N42" t="n">
-        <v>0.5969943496555853</v>
+        <v>0.6848263248813695</v>
       </c>
       <c r="O42" t="n">
-        <v>0.1189369449868934</v>
+        <v>0.09874968440628715</v>
       </c>
       <c r="P42" t="n">
-        <v>6.590099035898018</v>
+        <v>5.674226059447543</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.6273235353056051</v>
+        <v>0.6857435336491405</v>
       </c>
       <c r="R42" t="n">
-        <v>9.187271008566258</v>
+        <v>8.13164090172701</v>
       </c>
       <c r="S42" t="n">
-        <v>1.137123692401982</v>
+        <v>1.353269477552858</v>
       </c>
       <c r="T42" t="n">
-        <v>0.3433143602295701</v>
+        <v>0.2724155429586185</v>
       </c>
       <c r="U42" t="inlineStr">
         <is>
@@ -7066,71 +7070,71 @@
         </is>
       </c>
       <c r="W42" t="n">
-        <v>0.4896244345160509</v>
+        <v>0.4674738058780615</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>HistGradientBoosting</t>
+          <t>ExtraTrees</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.9444013295709164</v>
+        <v>0.9669113937672386</v>
       </c>
       <c r="C43" t="n">
-        <v>0.005400706334494193</v>
+        <v>0.01244938977036973</v>
       </c>
       <c r="D43" t="n">
-        <v>2.485619991371149</v>
+        <v>1.539096371877975</v>
       </c>
       <c r="E43" t="n">
-        <v>0.1744497368336272</v>
+        <v>0.3102962432987859</v>
       </c>
       <c r="F43" t="n">
-        <v>3.416612966075485</v>
+        <v>2.590198230043537</v>
       </c>
       <c r="G43" t="n">
-        <v>0.2083162803813793</v>
+        <v>0.5384126662620944</v>
       </c>
       <c r="H43" t="n">
-        <v>0.4896244345160509</v>
+        <v>0.4674738058780615</v>
       </c>
       <c r="I43" t="n">
-        <v>0.1306622832103632</v>
+        <v>0.02602019720937696</v>
       </c>
       <c r="J43" t="n">
-        <v>7.912748836166595</v>
+        <v>8.146818796769816</v>
       </c>
       <c r="K43" t="n">
-        <v>1.237782810694867</v>
+        <v>1.682385810803282</v>
       </c>
       <c r="L43" t="n">
-        <v>10.92799431475202</v>
+        <v>11.51860687826882</v>
       </c>
       <c r="M43" t="n">
-        <v>1.601941552358581</v>
+        <v>2.678585938312185</v>
       </c>
       <c r="N43" t="n">
-        <v>0.420932608916461</v>
+        <v>0.5273940608703354</v>
       </c>
       <c r="O43" t="n">
-        <v>0.1224986386032733</v>
+        <v>0.1015331564633598</v>
       </c>
       <c r="P43" t="n">
-        <v>7.854260039497444</v>
+        <v>6.847290475142327</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.11250312193315</v>
+        <v>0.9974028610641616</v>
       </c>
       <c r="R43" t="n">
-        <v>11.00794231653457</v>
+        <v>10.06538473937215</v>
       </c>
       <c r="S43" t="n">
-        <v>1.573874735309052</v>
+        <v>2.138241119397775</v>
       </c>
       <c r="T43" t="n">
-        <v>0.5234687206544554</v>
+        <v>0.4395173328969032</v>
       </c>
       <c r="U43" t="inlineStr">
         <is>
@@ -7143,71 +7147,71 @@
         </is>
       </c>
       <c r="W43" t="n">
-        <v>0.4896244345160509</v>
+        <v>0.4674738058780615</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>PLS</t>
+          <t>HistGradientBoosting</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.32156015084811</v>
+        <v>0.9837875481272106</v>
       </c>
       <c r="C44" t="n">
-        <v>0.04429380736444474</v>
+        <v>0.003564915183516335</v>
       </c>
       <c r="D44" t="n">
-        <v>9.536031817695534</v>
+        <v>1.284018180753048</v>
       </c>
       <c r="E44" t="n">
-        <v>0.3798217563544996</v>
+        <v>0.1137317150903464</v>
       </c>
       <c r="F44" t="n">
-        <v>12.4745473333047</v>
+        <v>1.913315626652745</v>
       </c>
       <c r="G44" t="n">
-        <v>0.4866628414064534</v>
+        <v>0.1869483753397264</v>
       </c>
       <c r="H44" t="n">
-        <v>-1.445119615434399e+19</v>
+        <v>0.6217191052479883</v>
       </c>
       <c r="I44" t="n">
-        <v>6.799377186483379e+19</v>
+        <v>0.1292204966389827</v>
       </c>
       <c r="J44" t="n">
-        <v>1643632876.161202</v>
+        <v>5.888880189161604</v>
       </c>
       <c r="K44" t="n">
-        <v>6865787548.643857</v>
+        <v>0.7865032995956079</v>
       </c>
       <c r="L44" t="n">
-        <v>12316775939.43469</v>
+        <v>8.452822020339749</v>
       </c>
       <c r="M44" t="n">
-        <v>51390590363.08985</v>
+        <v>1.338749023770892</v>
       </c>
       <c r="N44" t="n">
-        <v>-5.28110644844545e+18</v>
+        <v>0.6369000598097195</v>
       </c>
       <c r="O44" t="n">
-        <v>2.512247656535244e+19</v>
+        <v>0.1228123171905472</v>
       </c>
       <c r="P44" t="n">
-        <v>823699262.826767</v>
+        <v>6.073490325914944</v>
       </c>
       <c r="Q44" t="n">
-        <v>3127222014.144507</v>
+        <v>0.7670136159642518</v>
       </c>
       <c r="R44" t="n">
-        <v>6893469437.56127</v>
+        <v>8.702088023463638</v>
       </c>
       <c r="S44" t="n">
-        <v>26164054145.04655</v>
+        <v>1.25221345804524</v>
       </c>
       <c r="T44" t="n">
-        <v>5.28110644844545e+18</v>
+        <v>0.3468874883174911</v>
       </c>
       <c r="U44" t="inlineStr">
         <is>
@@ -7220,84 +7224,392 @@
         </is>
       </c>
       <c r="W44" t="n">
-        <v>-2.599645166871899e+19</v>
+        <v>0.4151206744959519</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
+          <t>HistGradientBoosting</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>0.9833352020078822</v>
+      </c>
+      <c r="C45" t="n">
+        <v>0.001583451196759383</v>
+      </c>
+      <c r="D45" t="n">
+        <v>1.229250549229688</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0.1262040365776355</v>
+      </c>
+      <c r="F45" t="n">
+        <v>1.872397522982171</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0.1360221267464576</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.420760778198593</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0.1672820055091187</v>
+      </c>
+      <c r="J45" t="n">
+        <v>8.181840546976318</v>
+      </c>
+      <c r="K45" t="n">
+        <v>1.187164654699675</v>
+      </c>
+      <c r="L45" t="n">
+        <v>11.57339695745968</v>
+      </c>
+      <c r="M45" t="n">
+        <v>1.580013759663862</v>
+      </c>
+      <c r="N45" t="n">
+        <v>0.4211181589952108</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0.1266309945060971</v>
+      </c>
+      <c r="P45" t="n">
+        <v>7.766328052453725</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>0.8855498692485111</v>
+      </c>
+      <c r="R45" t="n">
+        <v>10.98913472077277</v>
+      </c>
+      <c r="S45" t="n">
+        <v>1.478502311447729</v>
+      </c>
+      <c r="T45" t="n">
+        <v>0.5622170430126714</v>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>engineered_9</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>GroupKFold</t>
+        </is>
+      </c>
+      <c r="W45" t="n">
+        <v>0.4151206744959519</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
           <t>PLS</t>
         </is>
       </c>
-      <c r="B45" t="n">
+      <c r="B46" t="n">
+        <v>0.32156015084811</v>
+      </c>
+      <c r="C46" t="n">
+        <v>0.04429380736444474</v>
+      </c>
+      <c r="D46" t="n">
+        <v>9.536031817695534</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0.3798217563544996</v>
+      </c>
+      <c r="F46" t="n">
+        <v>12.4745473333047</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0.4866628414064534</v>
+      </c>
+      <c r="H46" t="n">
+        <v>-1.445119615434399e+19</v>
+      </c>
+      <c r="I46" t="n">
+        <v>6.799377186483379e+19</v>
+      </c>
+      <c r="J46" t="n">
+        <v>1643632876.161202</v>
+      </c>
+      <c r="K46" t="n">
+        <v>6865787548.643857</v>
+      </c>
+      <c r="L46" t="n">
+        <v>12316775939.43469</v>
+      </c>
+      <c r="M46" t="n">
+        <v>51390590363.08985</v>
+      </c>
+      <c r="N46" t="n">
+        <v>-5.28110644844545e+18</v>
+      </c>
+      <c r="O46" t="n">
+        <v>2.512247656535244e+19</v>
+      </c>
+      <c r="P46" t="n">
+        <v>823699262.826767</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>3127222014.144507</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6893469437.56127</v>
+      </c>
+      <c r="S46" t="n">
+        <v>26164054145.04655</v>
+      </c>
+      <c r="T46" t="n">
+        <v>5.28110644844545e+18</v>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>engineered_9</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>random_5x5</t>
+        </is>
+      </c>
+      <c r="W46" t="n">
+        <v>-2.599645166871899e+19</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>PLS</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
         <v>0.3231127150737823</v>
       </c>
-      <c r="C45" t="n">
+      <c r="C47" t="n">
         <v>0.03062264925640785</v>
       </c>
-      <c r="D45" t="n">
+      <c r="D47" t="n">
         <v>9.129920567627467</v>
       </c>
-      <c r="E45" t="n">
+      <c r="E47" t="n">
         <v>0.4804870440560445</v>
       </c>
-      <c r="F45" t="n">
+      <c r="F47" t="n">
         <v>11.9433665598859</v>
       </c>
-      <c r="G45" t="n">
+      <c r="G47" t="n">
         <v>0.7178190812874872</v>
       </c>
-      <c r="H45" t="n">
+      <c r="H47" t="n">
         <v>-2.599645166871899e+19</v>
       </c>
-      <c r="I45" t="n">
+      <c r="I47" t="n">
         <v>3.711823808161151e+19</v>
       </c>
-      <c r="J45" t="n">
+      <c r="J47" t="n">
         <v>6539913291.351749</v>
       </c>
-      <c r="K45" t="n">
+      <c r="K47" t="n">
         <v>8887421718.199669</v>
       </c>
-      <c r="L45" t="n">
+      <c r="L47" t="n">
         <v>49411041948.81211</v>
       </c>
-      <c r="M45" t="n">
+      <c r="M47" t="n">
         <v>67940095873.03123</v>
       </c>
-      <c r="N45" t="n">
+      <c r="N47" t="n">
         <v>-1.70930145458707e+20</v>
       </c>
-      <c r="O45" t="n">
+      <c r="O47" t="n">
         <v>3.418602909174141e+20</v>
       </c>
-      <c r="P45" t="n">
+      <c r="P47" t="n">
         <v>8209222413.637158</v>
       </c>
-      <c r="Q45" t="n">
+      <c r="Q47" t="n">
         <v>16418444806.23231</v>
       </c>
-      <c r="R45" t="n">
+      <c r="R47" t="n">
         <v>69172137505.49338</v>
       </c>
-      <c r="S45" t="n">
+      <c r="S47" t="n">
         <v>138344274983.3684</v>
       </c>
-      <c r="T45" t="n">
+      <c r="T47" t="n">
         <v>1.70930145458707e+20</v>
       </c>
-      <c r="U45" t="inlineStr">
+      <c r="U47" t="inlineStr">
         <is>
           <t>engineered_9</t>
         </is>
       </c>
-      <c r="V45" t="inlineStr">
+      <c r="V47" t="inlineStr">
         <is>
           <t>GroupKFold</t>
         </is>
       </c>
-      <c r="W45" t="n">
+      <c r="W47" t="n">
         <v>-2.599645166871899e+19</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>MLP</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>0.6769089710557195</v>
+      </c>
+      <c r="C48" t="n">
+        <v>0.07127577025406881</v>
+      </c>
+      <c r="D48" t="n">
+        <v>6.277506467450731</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0.6661637245511932</v>
+      </c>
+      <c r="F48" t="n">
+        <v>8.536521094644991</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0.8889608281543521</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0.3679989433808597</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0.1970704673785026</v>
+      </c>
+      <c r="J48" t="n">
+        <v>8.132815970563129</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0.9133746992505605</v>
+      </c>
+      <c r="L48" t="n">
+        <v>11.02532088734411</v>
+      </c>
+      <c r="M48" t="n">
+        <v>1.702944188820309</v>
+      </c>
+      <c r="N48" t="n">
+        <v>0.3703929762188622</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0.200924224171402</v>
+      </c>
+      <c r="P48" t="n">
+        <v>8.291229329434778</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>0.9938231230478134</v>
+      </c>
+      <c r="R48" t="n">
+        <v>11.4357607572345</v>
+      </c>
+      <c r="S48" t="n">
+        <v>1.587455073899609</v>
+      </c>
+      <c r="T48" t="n">
+        <v>0.3065159948368573</v>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>engineered_9</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>random_5x5</t>
+        </is>
+      </c>
+      <c r="W48" t="n">
+        <v>0.3528294414796517</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>MLP</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>0.7306513646070573</v>
+      </c>
+      <c r="C49" t="n">
+        <v>0.05912339319895144</v>
+      </c>
+      <c r="D49" t="n">
+        <v>5.453627990490167</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0.686275570184088</v>
+      </c>
+      <c r="F49" t="n">
+        <v>7.473043349978076</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0.7240180660698285</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.1646270762764721</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0.2952668195594098</v>
+      </c>
+      <c r="J49" t="n">
+        <v>10.00615658502243</v>
+      </c>
+      <c r="K49" t="n">
+        <v>1.379385671897435</v>
+      </c>
+      <c r="L49" t="n">
+        <v>13.76775667215898</v>
+      </c>
+      <c r="M49" t="n">
+        <v>2.143227441402234</v>
+      </c>
+      <c r="N49" t="n">
+        <v>0.3118009806033628</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0.3156228221010601</v>
+      </c>
+      <c r="P49" t="n">
+        <v>8.541149293742226</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>2.103250626215035</v>
+      </c>
+      <c r="R49" t="n">
+        <v>11.78034346255622</v>
+      </c>
+      <c r="S49" t="n">
+        <v>2.931121969504886</v>
+      </c>
+      <c r="T49" t="n">
+        <v>0.4188503840036945</v>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>engineered_9</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>GroupKFold</t>
+        </is>
+      </c>
+      <c r="W49" t="n">
+        <v>0.3528294414796517</v>
       </c>
     </row>
   </sheetData>
@@ -7311,7 +7623,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7359,23 +7671,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>engineered_12</t>
+          <t>engineered_9</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.5377833642992098</v>
+        <v>0.5273940608703354</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1091862212118263</v>
+        <v>0.1015331564633598</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4860327627622528</v>
+        <v>0.4674738058780615</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9705875927978896</v>
+        <v>0.9669113937672386</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4328042284986798</v>
+        <v>0.4395173328969032</v>
       </c>
     </row>
     <row r="3">
@@ -7462,7 +7774,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>HistGradientBoosting</t>
+          <t>LightGBM</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -7471,79 +7783,79 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.4544702399216466</v>
+        <v>0.4438988428388094</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1345335989989198</v>
+        <v>0.1771144196941885</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5049815979134623</v>
+        <v>0.5332913988252597</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9871179195111625</v>
+        <v>0.9738225538896298</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5326476795895159</v>
+        <v>0.5299237110508204</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>LightGBM</t>
+          <t>Random Forest</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>engineered_12</t>
+          <t>engineered_9</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.4438988428388094</v>
+        <v>0.4322458312992719</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1771144196941885</v>
+        <v>0.09104362334831959</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5332913988252597</v>
+        <v>0.4014326148459689</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9738225538896298</v>
+        <v>0.9301658069812266</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5299237110508204</v>
+        <v>0.4979199756819547</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Random Forest</t>
+          <t>HistGradientBoosting</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>engineered_9</t>
+          <t>engineered_12</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.4322458312992719</v>
+        <v>0.4281417063439478</v>
       </c>
       <c r="D8" t="n">
-        <v>0.09104362334831959</v>
+        <v>0.09729795235118779</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4014326148459689</v>
+        <v>0.422902621141039</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9301658069812266</v>
+        <v>0.9692005410221173</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4979199756819547</v>
+        <v>0.5410588346781695</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GaussianProcess</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -7552,25 +7864,25 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.4215082016471047</v>
+        <v>0.4174013507683088</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1534240783063387</v>
+        <v>0.1230038695243832</v>
       </c>
       <c r="E9" t="n">
-        <v>0.338739223385862</v>
+        <v>0.4272038788816889</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9387964054919982</v>
+        <v>0.9820183301924155</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5172882038448935</v>
+        <v>0.5646169794241067</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>XGBoost</t>
+          <t>GaussianProcess</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -7579,19 +7891,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.4174013507683088</v>
+        <v>0.4152400171443699</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1230038695243832</v>
+        <v>0.1597148620644397</v>
       </c>
       <c r="E10" t="n">
-        <v>0.4272038788816889</v>
+        <v>0.372970863970061</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9820183301924155</v>
+        <v>0.925113059289898</v>
       </c>
       <c r="G10" t="n">
-        <v>0.5646169794241067</v>
+        <v>0.509873042145528</v>
       </c>
     </row>
     <row r="11">
@@ -7624,7 +7936,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AdaBoost</t>
+          <t>MLP</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -7633,133 +7945,133 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.2424954348431182</v>
+        <v>0.3355019483982192</v>
       </c>
       <c r="D12" t="n">
-        <v>0.05141088229569388</v>
+        <v>0.4297125477812171</v>
       </c>
       <c r="E12" t="n">
-        <v>0.3178717663170819</v>
+        <v>0.3368738840332105</v>
       </c>
       <c r="F12" t="n">
-        <v>0.708926643956496</v>
+        <v>0.9821531677069449</v>
       </c>
       <c r="G12" t="n">
-        <v>0.4664312091133778</v>
+        <v>0.6466512193087257</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Ridge+Poly</t>
+          <t>AdaBoost</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>engineered_9</t>
+          <t>engineered_12</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>-9.844493573592266e+16</v>
+        <v>0.2424954348431182</v>
       </c>
       <c r="D13" t="n">
-        <v>1.968898714718453e+17</v>
+        <v>0.05141088229569388</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.072922916415649e+20</v>
+        <v>0.3178717663170819</v>
       </c>
       <c r="F13" t="n">
-        <v>0.5723953700531301</v>
+        <v>0.708926643956496</v>
       </c>
       <c r="G13" t="n">
-        <v>9.844493573592266e+16</v>
+        <v>0.4664312091133778</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>PLS</t>
+          <t>Ridge+Poly</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>engineered_12</t>
+          <t>engineered_9</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>-1.017337186779134e+17</v>
+        <v>-9.844493573592266e+16</v>
       </c>
       <c r="D14" t="n">
-        <v>2.034674373558269e+17</v>
+        <v>1.968898714718453e+17</v>
       </c>
       <c r="E14" t="n">
-        <v>-4.460914288255418e+19</v>
+        <v>-1.072922916415649e+20</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2191928773218662</v>
+        <v>0.5723953700531301</v>
       </c>
       <c r="G14" t="n">
-        <v>1.017337186779134e+17</v>
+        <v>9.844493573592266e+16</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ElasticNet</t>
+          <t>PLS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>engineered_9</t>
+          <t>engineered_12</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>-1.312899313230605e+19</v>
+        <v>-1.017337186779134e+17</v>
       </c>
       <c r="D15" t="n">
-        <v>2.62579862646121e+19</v>
+        <v>2.034674373558269e+17</v>
       </c>
       <c r="E15" t="n">
-        <v>0.09671526165271145</v>
+        <v>-4.460914288255418e+19</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2900397654416775</v>
+        <v>0.2191928773218662</v>
       </c>
       <c r="G15" t="n">
-        <v>1.312899313230605e+19</v>
+        <v>1.017337186779134e+17</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Lasso</t>
+          <t>ElasticNet</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>engineered_12</t>
+          <t>engineered_9</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>-2.601593224341503e+19</v>
+        <v>-1.312899313230605e+19</v>
       </c>
       <c r="D16" t="n">
-        <v>5.203186448683006e+19</v>
+        <v>2.62579862646121e+19</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1189843839542996</v>
+        <v>0.09671526165271145</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3507025098188154</v>
+        <v>0.2900397654416775</v>
       </c>
       <c r="G16" t="n">
-        <v>2.601593224341503e+19</v>
+        <v>1.312899313230605e+19</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Ridge</t>
+          <t>Lasso</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7768,45 +8080,72 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>-3.651176760113215e+19</v>
+        <v>-2.601593224341503e+19</v>
       </c>
       <c r="D17" t="n">
-        <v>7.302353520226432e+19</v>
+        <v>5.203186448683006e+19</v>
       </c>
       <c r="E17" t="n">
-        <v>-6.279731491631379e+18</v>
+        <v>0.1189843839542996</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3375163731885609</v>
+        <v>0.3507025098188154</v>
       </c>
       <c r="G17" t="n">
-        <v>3.651176760113215e+19</v>
+        <v>2.601593224341503e+19</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>Ridge</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>engineered_12</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>-3.651176760113215e+19</v>
+      </c>
+      <c r="D18" t="n">
+        <v>7.302353520226432e+19</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-6.279731491631379e+18</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.3375163731885609</v>
+      </c>
+      <c r="G18" t="n">
+        <v>3.651176760113215e+19</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>BayesianRidge</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>engineered_9</t>
         </is>
       </c>
-      <c r="C18" t="n">
+      <c r="C19" t="n">
         <v>-1.025208226003857e+20</v>
       </c>
-      <c r="D18" t="n">
+      <c r="D19" t="n">
         <v>2.050416452007713e+20</v>
       </c>
-      <c r="E18" t="n">
+      <c r="E19" t="n">
         <v>-2.971698601396009e+19</v>
       </c>
-      <c r="F18" t="n">
+      <c r="F19" t="n">
         <v>0.3371445890258222</v>
       </c>
-      <c r="G18" t="n">
+      <c r="G19" t="n">
         <v>1.025208226003857e+20</v>
       </c>
     </row>
@@ -7821,7 +8160,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB23"/>
+  <dimension ref="A1:AH25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7963,6 +8302,36 @@
       <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>n_components</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>n_layers</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>units_l0</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>units_l1</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>activation</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>learning_rate_init</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>batch_size</t>
         </is>
       </c>
     </row>
@@ -8005,6 +8374,12 @@
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -8045,6 +8420,12 @@
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -8087,6 +8468,12 @@
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -8131,6 +8518,12 @@
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -8177,6 +8570,12 @@
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8190,7 +8589,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.096495</v>
+        <v>0.09912700000000001</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
@@ -8200,10 +8599,10 @@
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="n">
-        <v>0.417319</v>
+        <v>0.9824889999999999</v>
       </c>
       <c r="L7" t="n">
-        <v>4.445811</v>
+        <v>0.08895699999999999</v>
       </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
@@ -8221,6 +8620,12 @@
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr"/>
       <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr"/>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -8265,6 +8670,12 @@
       <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="inlineStr"/>
       <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="inlineStr"/>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="inlineStr"/>
+      <c r="AH8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -8311,6 +8722,12 @@
       <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr"/>
       <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -8340,25 +8757,31 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>144</v>
+        <v>321</v>
       </c>
       <c r="T10" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="U10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V10" t="n">
         <v>1</v>
       </c>
       <c r="W10" t="n">
-        <v>0.950982</v>
+        <v>0.9616209999999999</v>
       </c>
       <c r="X10" t="inlineStr"/>
       <c r="Y10" t="inlineStr"/>
       <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="inlineStr"/>
       <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="inlineStr"/>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="inlineStr"/>
+      <c r="AH10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -8389,26 +8812,32 @@
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr"/>
       <c r="T11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="n">
-        <v>455</v>
+        <v>318</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.042303</v>
+        <v>0.054002</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.005945</v>
+        <v>0.011762</v>
       </c>
       <c r="AA11" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="inlineStr"/>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="inlineStr"/>
+      <c r="AH11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -8449,20 +8878,26 @@
       <c r="AB12" t="n">
         <v>1</v>
       </c>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr"/>
+      <c r="AE12" t="inlineStr"/>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="inlineStr"/>
+      <c r="AH12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>engineered_9</t>
+          <t>engineered_12</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ridge</t>
+          <t>MLP</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>99.10015</v>
+        <v>0.000824</v>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
@@ -8489,6 +8924,26 @@
       <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="inlineStr"/>
       <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>87</v>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>tanh</t>
+        </is>
+      </c>
+      <c r="AG13" t="n">
+        <v>0.004813</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -8498,11 +8953,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Lasso</t>
+          <t>Ridge</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.663242</v>
+        <v>99.10015</v>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
@@ -8529,6 +8984,12 @@
       <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="inlineStr"/>
       <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="inlineStr"/>
+      <c r="AE14" t="inlineStr"/>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="inlineStr"/>
+      <c r="AH14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -8538,15 +8999,13 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ElasticNet</t>
+          <t>Lasso</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.967014</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0.837095</v>
-      </c>
+        <v>0.663242</v>
+      </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
@@ -8571,6 +9030,12 @@
       <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="inlineStr"/>
       <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr"/>
+      <c r="AD15" t="inlineStr"/>
+      <c r="AE15" t="inlineStr"/>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="inlineStr"/>
+      <c r="AH15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -8580,19 +9045,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Ridge+Poly</t>
+          <t>ElasticNet</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>98.212818</v>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="n">
-        <v>2</v>
-      </c>
-      <c r="F16" t="b">
-        <v>1</v>
-      </c>
+        <v>0.967014</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.837095</v>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
@@ -8615,6 +9078,12 @@
       <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="inlineStr"/>
       <c r="AB16" t="inlineStr"/>
+      <c r="AC16" t="inlineStr"/>
+      <c r="AD16" t="inlineStr"/>
+      <c r="AE16" t="inlineStr"/>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="inlineStr"/>
+      <c r="AH16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -8624,25 +9093,23 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>BayesianRidge</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr"/>
+          <t>Ridge+Poly</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>98.212818</v>
+      </c>
       <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="n">
-        <v>0.000239</v>
-      </c>
-      <c r="H17" t="n">
-        <v>1e-06</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0.000987</v>
-      </c>
-      <c r="J17" t="n">
-        <v>3e-06</v>
-      </c>
+      <c r="E17" t="n">
+        <v>2</v>
+      </c>
+      <c r="F17" t="b">
+        <v>1</v>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
@@ -8661,6 +9128,12 @@
       <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="inlineStr"/>
       <c r="AB17" t="inlineStr"/>
+      <c r="AC17" t="inlineStr"/>
+      <c r="AD17" t="inlineStr"/>
+      <c r="AE17" t="inlineStr"/>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="inlineStr"/>
+      <c r="AH17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -8670,25 +9143,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>GaussianProcess</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>0.003078</v>
-      </c>
+          <t>BayesianRidge</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="n">
-        <v>0.190052</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0.625454</v>
-      </c>
+      <c r="G18" t="n">
+        <v>0.000239</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1e-06</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.000987</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3e-06</v>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
@@ -8705,6 +9180,12 @@
       <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="inlineStr"/>
       <c r="AB18" t="inlineStr"/>
+      <c r="AC18" t="inlineStr"/>
+      <c r="AD18" t="inlineStr"/>
+      <c r="AE18" t="inlineStr"/>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="inlineStr"/>
+      <c r="AH18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -8714,10 +9195,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SVR_RBF</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr"/>
+          <t>GaussianProcess</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>0.014558</v>
+      </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
@@ -8725,17 +9208,15 @@
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="n">
-        <v>99.99455</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0.105317</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0.032648</v>
-      </c>
+      <c r="K19" t="n">
+        <v>0.158667</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.001188</v>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
@@ -8749,6 +9230,12 @@
       <c r="Z19" t="inlineStr"/>
       <c r="AA19" t="inlineStr"/>
       <c r="AB19" t="inlineStr"/>
+      <c r="AC19" t="inlineStr"/>
+      <c r="AD19" t="inlineStr"/>
+      <c r="AE19" t="inlineStr"/>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="inlineStr"/>
+      <c r="AH19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -8758,7 +9245,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>SVR_RBF</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
@@ -8771,20 +9258,18 @@
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>distance</t>
-        </is>
-      </c>
-      <c r="R20" t="n">
-        <v>2</v>
-      </c>
+      <c r="M20" t="n">
+        <v>99.99455</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.105317</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.032648</v>
+      </c>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr"/>
       <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr"/>
@@ -8795,6 +9280,12 @@
       <c r="Z20" t="inlineStr"/>
       <c r="AA20" t="inlineStr"/>
       <c r="AB20" t="inlineStr"/>
+      <c r="AC20" t="inlineStr"/>
+      <c r="AD20" t="inlineStr"/>
+      <c r="AE20" t="inlineStr"/>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="inlineStr"/>
+      <c r="AH20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -8804,7 +9295,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ExtraTrees</t>
+          <t>KNN</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
@@ -8820,29 +9311,33 @@
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr"/>
-      <c r="S21" t="n">
-        <v>142</v>
-      </c>
-      <c r="T21" t="n">
-        <v>12</v>
-      </c>
-      <c r="U21" t="n">
+      <c r="P21" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>distance</t>
+        </is>
+      </c>
+      <c r="R21" t="n">
         <v>2</v>
       </c>
-      <c r="V21" t="n">
-        <v>1</v>
-      </c>
-      <c r="W21" t="n">
-        <v>0.603633</v>
-      </c>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr"/>
       <c r="X21" t="inlineStr"/>
       <c r="Y21" t="inlineStr"/>
       <c r="Z21" t="inlineStr"/>
       <c r="AA21" t="inlineStr"/>
       <c r="AB21" t="inlineStr"/>
+      <c r="AC21" t="inlineStr"/>
+      <c r="AD21" t="inlineStr"/>
+      <c r="AE21" t="inlineStr"/>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="inlineStr"/>
+      <c r="AH21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -8852,7 +9347,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>HistGradientBoosting</t>
+          <t>ExtraTrees</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
@@ -8871,28 +9366,32 @@
       <c r="P22" t="inlineStr"/>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr"/>
-      <c r="S22" t="inlineStr"/>
+      <c r="S22" t="n">
+        <v>377</v>
+      </c>
       <c r="T22" t="n">
+        <v>12</v>
+      </c>
+      <c r="U22" t="n">
         <v>2</v>
       </c>
-      <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>5</v>
-      </c>
-      <c r="W22" t="inlineStr"/>
-      <c r="X22" t="n">
-        <v>649</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>0.107574</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>58</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0.935164</v>
+      </c>
+      <c r="X22" t="inlineStr"/>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr"/>
+      <c r="AA22" t="inlineStr"/>
       <c r="AB22" t="inlineStr"/>
+      <c r="AC22" t="inlineStr"/>
+      <c r="AD22" t="inlineStr"/>
+      <c r="AE22" t="inlineStr"/>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="inlineStr"/>
+      <c r="AH22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -8902,7 +9401,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>PLS</t>
+          <t>HistGradientBoosting</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
@@ -8922,16 +9421,138 @@
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr"/>
-      <c r="T23" t="inlineStr"/>
+      <c r="T23" t="n">
+        <v>3</v>
+      </c>
       <c r="U23" t="inlineStr"/>
-      <c r="V23" t="inlineStr"/>
+      <c r="V23" t="n">
+        <v>5</v>
+      </c>
       <c r="W23" t="inlineStr"/>
-      <c r="X23" t="inlineStr"/>
-      <c r="Y23" t="inlineStr"/>
-      <c r="Z23" t="inlineStr"/>
-      <c r="AA23" t="inlineStr"/>
-      <c r="AB23" t="n">
+      <c r="X23" t="n">
+        <v>374</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0.186155</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>0.08677700000000001</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>28</v>
+      </c>
+      <c r="AB23" t="inlineStr"/>
+      <c r="AC23" t="inlineStr"/>
+      <c r="AD23" t="inlineStr"/>
+      <c r="AE23" t="inlineStr"/>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="inlineStr"/>
+      <c r="AH23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>engineered_9</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>PLS</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr"/>
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr"/>
+      <c r="AB24" t="n">
         <v>2</v>
+      </c>
+      <c r="AC24" t="inlineStr"/>
+      <c r="AD24" t="inlineStr"/>
+      <c r="AE24" t="inlineStr"/>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="inlineStr"/>
+      <c r="AH24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>engineered_9</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>MLP</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>2.6e-05</v>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr"/>
+      <c r="X25" t="inlineStr"/>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr"/>
+      <c r="AB25" t="inlineStr"/>
+      <c r="AC25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>95</v>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>tanh</t>
+        </is>
+      </c>
+      <c r="AG25" t="n">
+        <v>0.000558</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -9067,61 +9688,61 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9603476604186858</v>
+        <v>0.9462907710930339</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01552474354434908</v>
+        <v>0.01840179092253964</v>
       </c>
       <c r="D2" t="n">
-        <v>1.893879976231422</v>
+        <v>2.251561928156972</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3125167255559717</v>
+        <v>0.3190954532054868</v>
       </c>
       <c r="F2" t="n">
-        <v>2.963314073235102</v>
+        <v>3.46269019903715</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5888656498375247</v>
+        <v>0.6005521495543439</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6840137193030799</v>
+        <v>0.6798574643486377</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1182874176167537</v>
+        <v>0.1175080679832402</v>
       </c>
       <c r="J2" t="n">
-        <v>5.382731338743322</v>
+        <v>5.462223755937718</v>
       </c>
       <c r="K2" t="n">
-        <v>0.6977125878767364</v>
+        <v>0.7220307625118233</v>
       </c>
       <c r="L2" t="n">
-        <v>7.723496195698348</v>
+        <v>7.780402412521227</v>
       </c>
       <c r="M2" t="n">
-        <v>1.362045001613021</v>
+        <v>1.34870926396425</v>
       </c>
       <c r="N2" t="n">
-        <v>0.7101986963326762</v>
+        <v>0.7030189472874318</v>
       </c>
       <c r="O2" t="n">
-        <v>0.09567849083637209</v>
+        <v>0.09769981895736926</v>
       </c>
       <c r="P2" t="n">
-        <v>5.36870363108912</v>
+        <v>5.473919115250758</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.6688831538720473</v>
+        <v>0.7067685962198056</v>
       </c>
       <c r="R2" t="n">
-        <v>7.786880006524891</v>
+        <v>7.885498558373859</v>
       </c>
       <c r="S2" t="n">
-        <v>1.280169078492063</v>
+        <v>1.294661713544667</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2501489640860096</v>
+        <v>0.2432718238056022</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -9141,61 +9762,61 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9212662999192112</v>
+        <v>0.9129833461859425</v>
       </c>
       <c r="C3" t="n">
-        <v>0.03752743172348962</v>
+        <v>0.03885692168554399</v>
       </c>
       <c r="D3" t="n">
-        <v>2.791158546619081</v>
+        <v>2.906895239530906</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5793509401064899</v>
+        <v>0.6109987555108655</v>
       </c>
       <c r="F3" t="n">
-        <v>3.964468691704439</v>
+        <v>4.183867660251865</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9100034923754797</v>
+        <v>0.953466710968513</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5427715643910115</v>
+        <v>0.514581786354013</v>
       </c>
       <c r="I3" t="n">
-        <v>0.05847957930926902</v>
+        <v>0.07788633403713612</v>
       </c>
       <c r="J3" t="n">
-        <v>7.567772050777376</v>
+        <v>7.78952838781718</v>
       </c>
       <c r="K3" t="n">
-        <v>1.48337118334615</v>
+        <v>1.346832967402374</v>
       </c>
       <c r="L3" t="n">
-        <v>10.54930365110181</v>
+        <v>10.78520603968713</v>
       </c>
       <c r="M3" t="n">
-        <v>2.043799703880252</v>
+        <v>1.811995743931109</v>
       </c>
       <c r="N3" t="n">
-        <v>0.5226626134430703</v>
+        <v>0.5212331659450371</v>
       </c>
       <c r="O3" t="n">
-        <v>0.171494355186565</v>
+        <v>0.1604585083178662</v>
       </c>
       <c r="P3" t="n">
-        <v>6.909555206286498</v>
+        <v>6.95288683137812</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.255524839443108</v>
+        <v>1.213997093491492</v>
       </c>
       <c r="R3" t="n">
-        <v>9.908043504942771</v>
+        <v>9.942139836428268</v>
       </c>
       <c r="S3" t="n">
-        <v>2.176924830221316</v>
+        <v>2.014466403952702</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3986036864761409</v>
+        <v>0.3917501802409054</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -9489,61 +10110,61 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9650939611372451</v>
+        <v>0.9345562112534603</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01118938556706166</v>
+        <v>0.01654371163717382</v>
       </c>
       <c r="D4" t="n">
-        <v>1.59896928984357</v>
+        <v>2.48843645924844</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2171979751722178</v>
+        <v>0.2529856216604573</v>
       </c>
       <c r="F4" t="n">
-        <v>2.772312498076556</v>
+        <v>3.81694946712485</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4466153575721635</v>
+        <v>0.4763358643232536</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6744449954863801</v>
+        <v>0.6568704123368059</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1261529717501174</v>
+        <v>0.1276705490184939</v>
       </c>
       <c r="J4" t="n">
-        <v>5.610751183192084</v>
+        <v>5.91117359020609</v>
       </c>
       <c r="K4" t="n">
-        <v>0.686301150782564</v>
+        <v>0.6693136277384231</v>
       </c>
       <c r="L4" t="n">
-        <v>8.026023520002493</v>
+        <v>8.243380690066592</v>
       </c>
       <c r="M4" t="n">
-        <v>1.412794929787874</v>
+        <v>1.384960663087976</v>
       </c>
       <c r="N4" t="n">
-        <v>0.6936060922106397</v>
+        <v>0.6750008760063723</v>
       </c>
       <c r="O4" t="n">
-        <v>0.09177860117459496</v>
+        <v>0.09601213649441445</v>
       </c>
       <c r="P4" t="n">
-        <v>5.525075720994129</v>
+        <v>5.779042879295448</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.5275877993770122</v>
+        <v>0.5661390298430216</v>
       </c>
       <c r="R4" t="n">
-        <v>7.979817300521128</v>
+        <v>8.222196384319188</v>
       </c>
       <c r="S4" t="n">
-        <v>1.095179657063009</v>
+        <v>1.091789390950408</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2714878689266054</v>
+        <v>0.2595553352470881</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -9563,61 +10184,61 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9705875927978896</v>
+        <v>0.9455634610237889</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01192338159101609</v>
+        <v>0.01632833395300252</v>
       </c>
       <c r="D5" t="n">
-        <v>1.430205808478588</v>
+        <v>2.224633279735309</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3354928134464878</v>
+        <v>0.3531374158462773</v>
       </c>
       <c r="F5" t="n">
-        <v>2.428309957409171</v>
+        <v>3.350024415890302</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5802568756561601</v>
+        <v>0.6098193975392179</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4860327627622528</v>
+        <v>0.4844628548595775</v>
       </c>
       <c r="I5" t="n">
-        <v>0.04156134132379476</v>
+        <v>0.04643833666270597</v>
       </c>
       <c r="J5" t="n">
-        <v>8.081629961970981</v>
+        <v>8.143488012765442</v>
       </c>
       <c r="K5" t="n">
-        <v>2.032668102478756</v>
+        <v>2.012852221874569</v>
       </c>
       <c r="L5" t="n">
-        <v>11.39003410551051</v>
+        <v>11.39282741155926</v>
       </c>
       <c r="M5" t="n">
-        <v>2.978725246373724</v>
+        <v>2.932355931551956</v>
       </c>
       <c r="N5" t="n">
-        <v>0.5377833642992098</v>
+        <v>0.5120134711810558</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1091862212118263</v>
+        <v>0.1006634687822661</v>
       </c>
       <c r="P5" t="n">
-        <v>6.795611432910858</v>
+        <v>7.065385808263474</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9135015440495705</v>
+        <v>1.024059879551301</v>
       </c>
       <c r="R5" t="n">
-        <v>9.921059862515415</v>
+        <v>10.21721804683181</v>
       </c>
       <c r="S5" t="n">
-        <v>2.071290892780488</v>
+        <v>2.084793641690672</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4328042284986798</v>
+        <v>0.4335499898427331</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -9785,61 +10406,61 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.9856430056160062</v>
+        <v>0.9679799657984518</v>
       </c>
       <c r="C8" t="n">
-        <v>0.002782029602668497</v>
+        <v>0.00649314982867918</v>
       </c>
       <c r="D8" t="n">
-        <v>1.2645454136252</v>
+        <v>1.920553712024816</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1019179921228466</v>
+        <v>0.1416569984910656</v>
       </c>
       <c r="F8" t="n">
-        <v>1.793940938174822</v>
+        <v>2.676145582756372</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1407077333995984</v>
+        <v>0.2249117631472435</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6433402074023461</v>
+        <v>0.6343544806439795</v>
       </c>
       <c r="I8" t="n">
-        <v>0.138821932963102</v>
+        <v>0.1396860228915605</v>
       </c>
       <c r="J8" t="n">
-        <v>5.936531478317606</v>
+        <v>6.140579219885029</v>
       </c>
       <c r="K8" t="n">
-        <v>0.7727858445661958</v>
+        <v>0.7866501817780597</v>
       </c>
       <c r="L8" t="n">
-        <v>8.366594392759016</v>
+        <v>8.47042606105261</v>
       </c>
       <c r="M8" t="n">
-        <v>1.480747918926749</v>
+        <v>1.461884420522478</v>
       </c>
       <c r="N8" t="n">
-        <v>0.6577159714024995</v>
+        <v>0.6481401309935099</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1058588944619571</v>
+        <v>0.1030002653258887</v>
       </c>
       <c r="P8" t="n">
-        <v>5.905348165265294</v>
+        <v>6.090115925212381</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.6116382672392888</v>
+        <v>0.6086735057375647</v>
       </c>
       <c r="R8" t="n">
-        <v>8.446249303453314</v>
+        <v>8.583266637790961</v>
       </c>
       <c r="S8" t="n">
-        <v>1.080996875731679</v>
+        <v>1.042988179484481</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3279270342135067</v>
+        <v>0.3198398348049419</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
@@ -9859,61 +10480,61 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9871179195111625</v>
+        <v>0.9692005410221173</v>
       </c>
       <c r="C9" t="n">
-        <v>0.002359068158468191</v>
+        <v>0.006212534125556454</v>
       </c>
       <c r="D9" t="n">
-        <v>1.169967310286348</v>
+        <v>1.84106996046136</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1634976126932077</v>
+        <v>0.2333842008977969</v>
       </c>
       <c r="F9" t="n">
-        <v>1.642502606376544</v>
+        <v>2.535575827527034</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2010480749282015</v>
+        <v>0.2950102077098801</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5049815979134623</v>
+        <v>0.422902621141039</v>
       </c>
       <c r="I9" t="n">
-        <v>0.07576486186526878</v>
+        <v>0.1406711332008928</v>
       </c>
       <c r="J9" t="n">
-        <v>7.923917410125403</v>
+        <v>8.605448924157439</v>
       </c>
       <c r="K9" t="n">
-        <v>1.936217529553563</v>
+        <v>1.766215765966688</v>
       </c>
       <c r="L9" t="n">
-        <v>10.97981639024868</v>
+        <v>11.71197174282898</v>
       </c>
       <c r="M9" t="n">
-        <v>2.312190399651964</v>
+        <v>2.286752206087009</v>
       </c>
       <c r="N9" t="n">
-        <v>0.4544702399216466</v>
+        <v>0.4281417063439478</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1345335989989198</v>
+        <v>0.09729795235118779</v>
       </c>
       <c r="P9" t="n">
-        <v>7.543808145564974</v>
+        <v>7.827752113930683</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.286174227873372</v>
+        <v>0.9390066673454479</v>
       </c>
       <c r="R9" t="n">
-        <v>10.79578526937301</v>
+        <v>11.01082854408628</v>
       </c>
       <c r="S9" t="n">
-        <v>2.332243837764302</v>
+        <v>1.718763518611727</v>
       </c>
       <c r="T9" t="n">
-        <v>0.5326476795895159</v>
+        <v>0.5410588346781695</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
@@ -9937,7 +10558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:W13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9948,310 +10569,1030 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>SMOGN_group</t>
+          <t>train_r2_mean</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>SMOGN_random</t>
+          <t>train_r2_std</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>group_strict</t>
+          <t>train_mae_mean</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>random_KF</t>
+          <t>train_mae_std</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>train_rmse_mean</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>train_rmse_std</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>val_r2_mean</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>val_r2_std</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>val_mae_mean</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>val_mae_std</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>val_rmse_mean</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>val_rmse_std</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>test_r2_mean</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>test_r2_std</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>test_mae_mean</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>test_mae_std</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>test_rmse_mean</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>test_rmse_std</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>overfit_gap</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>feature_set</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>cv</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>best_optuna_val</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>AdaBoost</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>MLP_group_obj</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0.9753411197979568</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.01115192506325255</v>
+      </c>
       <c r="D2" t="n">
-        <v>0.2424954348431182</v>
+        <v>1.550996690678982</v>
       </c>
       <c r="E2" t="n">
-        <v>0.463419019492389</v>
+        <v>0.321683428716965</v>
+      </c>
+      <c r="F2" t="n">
+        <v>2.314352309126113</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.4940823584909748</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.5134801859276779</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.1531943028549214</v>
+      </c>
+      <c r="J2" t="n">
+        <v>6.633856325823493</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.709623132161472</v>
+      </c>
+      <c r="L2" t="n">
+        <v>9.585029235689177</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.194204687850827</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.511053070156766</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.2024638566875647</v>
+      </c>
+      <c r="P2" t="n">
+        <v>6.794052525644784</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.9157127415956129</v>
+      </c>
+      <c r="R2" t="n">
+        <v>9.991038029243583</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1.645179966831313</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.4642880496411907</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>engineered_12</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>random_5x5</t>
+        </is>
+      </c>
+      <c r="W2" t="n">
+        <v>0.3698460606321731</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>BayesianRidge</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>MLP_group_obj</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.9821531677069449</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.002015942007211611</v>
+      </c>
       <c r="D3" t="n">
-        <v>-1.025208226003857e+20</v>
+        <v>1.364461224048362</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.301642117577251e+19</v>
+        <v>0.01879894310199522</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1.931767267286485</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.07093042884423895</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.3368738840332105</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.2709023758495344</v>
+      </c>
+      <c r="J3" t="n">
+        <v>8.840861749816899</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1.522972296533523</v>
+      </c>
+      <c r="L3" t="n">
+        <v>12.30827682493659</v>
+      </c>
+      <c r="M3" t="n">
+        <v>2.160831217956384</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.3355019483982192</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.4297125477812171</v>
+      </c>
+      <c r="P3" t="n">
+        <v>7.891299962993109</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.496440678066479</v>
+      </c>
+      <c r="R3" t="n">
+        <v>11.16028015812556</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2.314954475443903</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.6466512193087257</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>engineered_12</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>GroupKFold</t>
+        </is>
+      </c>
+      <c r="W3" t="n">
+        <v>0.3698460606321731</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>CatBoost</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>MLP_random_obj</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.9464940306177629</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.01629868621287323</v>
+      </c>
       <c r="D4" t="n">
-        <v>0.518685299246141</v>
+        <v>2.277821915394061</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6800005703790878</v>
+        <v>0.3583159963330075</v>
+      </c>
+      <c r="F4" t="n">
+        <v>3.451728620222482</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.5317880865821618</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.534123839940874</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.1575653997844446</v>
+      </c>
+      <c r="J4" t="n">
+        <v>6.585841913357126</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.6831570135074791</v>
+      </c>
+      <c r="L4" t="n">
+        <v>9.395503097360551</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.346330465412763</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.592881926832985</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.145767019533158</v>
+      </c>
+      <c r="P4" t="n">
+        <v>6.362618464589323</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.8275960792224366</v>
+      </c>
+      <c r="R4" t="n">
+        <v>9.186902954851327</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1.377063376101532</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.3536121037847779</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>engineered_12</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>random_5x5</t>
+        </is>
+      </c>
+      <c r="W4" t="n">
+        <v>0.5856552237622972</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>ElasticNet</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>MLP_random_obj</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.9640365231764159</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.01004562052110548</v>
+      </c>
       <c r="D5" t="n">
-        <v>-1.312899313230605e+19</v>
+        <v>1.748316717056371</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2443330070411298</v>
+        <v>0.2306606600978599</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2.723118343099157</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.3738297001247949</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.339431935878347</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.2111127539293473</v>
+      </c>
+      <c r="J5" t="n">
+        <v>8.750160636732705</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1.678399940604439</v>
+      </c>
+      <c r="L5" t="n">
+        <v>12.40564703982362</v>
+      </c>
+      <c r="M5" t="n">
+        <v>2.647729506008953</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.5112760340309848</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.1934614452369844</v>
+      </c>
+      <c r="P5" t="n">
+        <v>7.059594199478672</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.020969303581403</v>
+      </c>
+      <c r="R5" t="n">
+        <v>9.963668616388228</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1.836008042912258</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.4527604891454311</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>engineered_12</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>GroupKFold</t>
+        </is>
+      </c>
+      <c r="W5" t="n">
+        <v>0.5856552237622972</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>ExtraTrees</t>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>MLP_seed_ensemble</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5377833642992098</v>
+        <v>0.9543939858120948</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6936060922106397</v>
+        <v>0.01356082074240657</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5377833642992098</v>
+        <v>1.965851432284491</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6977481385930541</v>
-      </c>
+        <v>0.2915827769641691</v>
+      </c>
+      <c r="F6" t="n">
+        <v>3.188616279166833</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.4728494399215942</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.5690242577318312</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.1361673840747712</v>
+      </c>
+      <c r="J6" t="n">
+        <v>6.282905757155651</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.6382800123988234</v>
+      </c>
+      <c r="L6" t="n">
+        <v>9.072357267173295</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.42512717719684</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.6011384294940464</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.1796342014306688</v>
+      </c>
+      <c r="P6" t="n">
+        <v>6.085880732846582</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.7771997285921755</v>
+      </c>
+      <c r="R6" t="n">
+        <v>9.002021867585885</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.575619291045034</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.3532555563180484</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>engineered_12</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>random_5x5</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>GaussianProcess</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>MLP_seed_ensemble</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.967721983559849</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.007908669785083894</v>
+      </c>
       <c r="D7" t="n">
-        <v>0.4215082016471047</v>
+        <v>1.561736877218064</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6318264138040046</v>
-      </c>
+        <v>0.2076609644194993</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2.584399177450024</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.3119842979813821</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.378866479918081</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.2201598787379025</v>
+      </c>
+      <c r="J7" t="n">
+        <v>8.684485573115484</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1.728625747342957</v>
+      </c>
+      <c r="L7" t="n">
+        <v>11.99709078028748</v>
+      </c>
+      <c r="M7" t="n">
+        <v>2.508642393051789</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.5194617222325817</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.2100125532535503</v>
+      </c>
+      <c r="P7" t="n">
+        <v>6.841560121514104</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.9625433728813336</v>
+      </c>
+      <c r="R7" t="n">
+        <v>9.809423922333258</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1.687651408650216</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.4482602613272673</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>engineered_12</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>GroupKFold</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Gradient Boosting</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>MLP_group_obj</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.6769089710557195</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.07127577025406881</v>
+      </c>
       <c r="D8" t="n">
-        <v>0.4814603090734479</v>
+        <v>6.277506467450731</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6789381943992349</v>
+        <v>0.6661637245511932</v>
+      </c>
+      <c r="F8" t="n">
+        <v>8.536521094644991</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.8889608281543521</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.3679989433808597</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.1970704673785026</v>
+      </c>
+      <c r="J8" t="n">
+        <v>8.132815970563129</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.9133746992505605</v>
+      </c>
+      <c r="L8" t="n">
+        <v>11.02532088734411</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.702944188820309</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.3703929762188622</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.200924224171402</v>
+      </c>
+      <c r="P8" t="n">
+        <v>8.291229329434778</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.9938231230478134</v>
+      </c>
+      <c r="R8" t="n">
+        <v>11.4357607572345</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.587455073899609</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.3065159948368573</v>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>engineered_9</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>random_5x5</t>
+        </is>
+      </c>
+      <c r="W8" t="n">
+        <v>0.3528294414796517</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>HistGradientBoosting</t>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>MLP_group_obj</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.4544702399216466</v>
+        <v>0.7306513646070573</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6577159714024995</v>
+        <v>0.05912339319895144</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4544702399216466</v>
+        <v>5.453627990490167</v>
       </c>
       <c r="E9" t="n">
-        <v>0.6526113161425383</v>
+        <v>0.686275570184088</v>
+      </c>
+      <c r="F9" t="n">
+        <v>7.473043349978076</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.7240180660698285</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.1646270762764721</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.2952668195594098</v>
+      </c>
+      <c r="J9" t="n">
+        <v>10.00615658502243</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1.379385671897435</v>
+      </c>
+      <c r="L9" t="n">
+        <v>13.76775667215898</v>
+      </c>
+      <c r="M9" t="n">
+        <v>2.143227441402234</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.3118009806033628</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.3156228221010601</v>
+      </c>
+      <c r="P9" t="n">
+        <v>8.541149293742226</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.103250626215035</v>
+      </c>
+      <c r="R9" t="n">
+        <v>11.78034346255622</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.931121969504886</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.4188503840036945</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>engineered_9</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>GroupKFold</t>
+        </is>
+      </c>
+      <c r="W9" t="n">
+        <v>0.3528294414796517</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>KNN</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>MLP_random_obj</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.9721583284399196</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.007549260043540528</v>
+      </c>
       <c r="D10" t="n">
-        <v>0.393041828052859</v>
+        <v>1.640334695047745</v>
       </c>
       <c r="E10" t="n">
-        <v>0.6164364310788732</v>
+        <v>0.2725575199384467</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2.505257299507647</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.3601330114144612</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.5133892046177908</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.1635824698319076</v>
+      </c>
+      <c r="J10" t="n">
+        <v>6.699939022222023</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.9410428639766208</v>
+      </c>
+      <c r="L10" t="n">
+        <v>9.583026052113002</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.409904004742971</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.5927846498831097</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.1106969690749498</v>
+      </c>
+      <c r="P10" t="n">
+        <v>6.41339060505695</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.5906118202494302</v>
+      </c>
+      <c r="R10" t="n">
+        <v>9.256066833802389</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1.132909493178555</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.3793736785568098</v>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>engineered_9</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>random_5x5</t>
+        </is>
+      </c>
+      <c r="W10" t="n">
+        <v>0.6049391785972887</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>Lasso</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>MLP_random_obj</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.9776664344598611</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.0040532185963473</v>
+      </c>
       <c r="D11" t="n">
-        <v>-2.601593224341503e+19</v>
+        <v>1.428762500517198</v>
       </c>
       <c r="E11" t="n">
-        <v>0.240953414114923</v>
+        <v>0.09260126591399286</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2.15235555677532</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.1694415823636674</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.3508440801910477</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.2253065986942846</v>
+      </c>
+      <c r="J11" t="n">
+        <v>8.683053754853493</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1.106485240644782</v>
+      </c>
+      <c r="L11" t="n">
+        <v>12.0774228928841</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.182332448339344</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.4081886900221489</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.2719144847519686</v>
+      </c>
+      <c r="P11" t="n">
+        <v>7.540929271792156</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.9530029420207184</v>
+      </c>
+      <c r="R11" t="n">
+        <v>10.77310596898333</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1.619079604714136</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0.5694777444377122</v>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>engineered_9</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>GroupKFold</t>
+        </is>
+      </c>
+      <c r="W11" t="n">
+        <v>0.6049391785972887</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>LightGBM</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>MLP_seed_ensemble</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.980695915597388</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.007007784612140185</v>
+      </c>
       <c r="D12" t="n">
-        <v>0.4438988428388094</v>
+        <v>1.140682018635927</v>
       </c>
       <c r="E12" t="n">
-        <v>0.6655718460950149</v>
-      </c>
+        <v>0.1905467416222453</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2.062524000476951</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.3839866788638132</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.5819003267924923</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.1343855037061591</v>
+      </c>
+      <c r="J12" t="n">
+        <v>6.117441639137434</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.8378497430984018</v>
+      </c>
+      <c r="L12" t="n">
+        <v>8.887681673181591</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.177467480864047</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.6323349391106788</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.1138520531600967</v>
+      </c>
+      <c r="P12" t="n">
+        <v>5.921032503617853</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.6322295282791098</v>
+      </c>
+      <c r="R12" t="n">
+        <v>8.75280968004158</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1.112879039977084</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0.3483609764867092</v>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>engineered_9</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>random_5x5</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>PLS</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>MLP_seed_ensemble</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.9835134909027186</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.003596491895114749</v>
+      </c>
       <c r="D13" t="n">
-        <v>-1.017337186779134e+17</v>
+        <v>1.032386999138083</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.28110644844545e+18</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>Random Forest</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="n">
-        <v>0.4322458312992719</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0.626259917054957</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>Ridge</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="n">
-        <v>-3.651176760113215e+19</v>
-      </c>
-      <c r="E15" t="n">
-        <v>-2.614720185200482e+18</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>Ridge+Poly</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="n">
-        <v>-9.844493573592266e+16</v>
-      </c>
-      <c r="E16" t="n">
-        <v>-3.560642177403972e+19</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>SVR_RBF</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>0.4727678796962161</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0.559565778843728</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0.5235726680511263</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0.6137629940723229</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>Stacked (SVR+ET+XGB+HGB)</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="n">
-        <v>0.5226626134430703</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0.7101986963326762</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>XGBoost</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>0.4103448982353368</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0.670262647318171</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0.4174013507683088</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0.6604985786262069</v>
-      </c>
+        <v>0.08362505881351004</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1.846772701933087</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.179776729415188</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.4076814856457509</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.1830702784331359</v>
+      </c>
+      <c r="J13" t="n">
+        <v>8.418015002962649</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1.410948583511087</v>
+      </c>
+      <c r="L13" t="n">
+        <v>11.66963734776971</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.703254545036563</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.4861593186236022</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.2314484522466891</v>
+      </c>
+      <c r="P13" t="n">
+        <v>6.996913035771864</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.197772388716217</v>
+      </c>
+      <c r="R13" t="n">
+        <v>10.11877235145942</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.081775061495159</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0.4973541722791163</v>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>engineered_9</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>GroupKFold</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10264,7 +11605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:V9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10275,309 +11616,1969 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>SMOGN_group</t>
+          <t>train_r2_mean</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>SMOGN_random</t>
+          <t>train_r2_std</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>group_strict</t>
+          <t>train_mae_mean</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>random_KF</t>
+          <t>train_mae_std</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>train_rmse_mean</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>train_rmse_std</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>val_r2_mean</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>val_r2_std</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>val_mae_mean</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>val_mae_std</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>val_rmse_mean</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>val_rmse_std</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>test_r2_mean</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>test_r2_std</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>test_mae_mean</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>test_mae_std</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>test_rmse_mean</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>test_rmse_std</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>overfit_gap</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>feature_set</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>cv</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>AdaBoost</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>BoostStack(GB+LGBM+CB+XGB+ET)</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0.9694316534145918</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.01653183177579512</v>
+      </c>
       <c r="D2" t="n">
-        <v>0.4664312091133778</v>
+        <v>1.708474181685737</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2363304310683094</v>
+        <v>0.3956665902736462</v>
+      </c>
+      <c r="F2" t="n">
+        <v>2.555606304554024</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.6714199396428779</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.6780211079818641</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.115690932322691</v>
+      </c>
+      <c r="J2" t="n">
+        <v>5.39864028899042</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.6692669586358438</v>
+      </c>
+      <c r="L2" t="n">
+        <v>7.800029729846177</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.338707085797781</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.7013662369195868</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.1014445556307475</v>
+      </c>
+      <c r="P2" t="n">
+        <v>5.45387221985503</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.6934509273413807</v>
+      </c>
+      <c r="R2" t="n">
+        <v>7.907896646062904</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1.347689352309576</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.268065416495005</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>engineered_12</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>random_5x5</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>BayesianRidge</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>BoostStack(GB+LGBM+CB+XGB+ET)</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.9498880514691548</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.01532628223004713</v>
+      </c>
       <c r="D3" t="n">
-        <v>1.025208226003857e+20</v>
+        <v>2.259956247758424</v>
       </c>
       <c r="E3" t="n">
-        <v>1.301642117577251e+19</v>
+        <v>0.3742507101950781</v>
+      </c>
+      <c r="F3" t="n">
+        <v>3.221064910489611</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.5658904820964986</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.5535553384935544</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.0704455476987889</v>
+      </c>
+      <c r="J3" t="n">
+        <v>7.452433908498662</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1.432868012850651</v>
+      </c>
+      <c r="L3" t="n">
+        <v>10.3848238891823</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.964249951075282</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.5165052899329102</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.1308016091003538</v>
+      </c>
+      <c r="P3" t="n">
+        <v>7.052888946643312</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.185817689681258</v>
+      </c>
+      <c r="R3" t="n">
+        <v>10.0727053560214</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1.989382403547476</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.4333827615362446</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>engineered_12</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>GroupKFold</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>GB_seed_ensemble(10)</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.9975993774015574</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.0006226287940916867</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.508702535204213</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.0612319931754934</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.7354441597084902</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.09373899272650101</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.6708459536286553</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.1158255164998154</v>
+      </c>
+      <c r="J4" t="n">
+        <v>5.363756046983935</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.7246918408072993</v>
+      </c>
+      <c r="L4" t="n">
+        <v>7.89028003459511</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.35839428625405</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.6932082172344949</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.1034711843468073</v>
+      </c>
+      <c r="P4" t="n">
+        <v>5.447460843649107</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.6393860892786188</v>
+      </c>
+      <c r="R4" t="n">
+        <v>8.020436348901798</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1.337064232140803</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.3043911601670625</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>engineered_12</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>random_5x5</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>GB_seed_ensemble(10)</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.9967745813967037</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.001030372052100682</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.5033383975624354</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.04314471484427938</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.8152325301437969</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.1397926418854654</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.4718634789315447</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.09670380261969094</v>
+      </c>
+      <c r="J5" t="n">
+        <v>8.080461370605326</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1.89842181922493</v>
+      </c>
+      <c r="L5" t="n">
+        <v>11.32069465415544</v>
+      </c>
+      <c r="M5" t="n">
+        <v>2.460346441710944</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.4588596716526047</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.1149441991659252</v>
+      </c>
+      <c r="P5" t="n">
+        <v>7.332741879519682</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.211119300732137</v>
+      </c>
+      <c r="R5" t="n">
+        <v>10.73571832565744</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.067362729550029</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.5379149097440991</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>engineered_12</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>GroupKFold</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>BoostStack(GB+LGBM+CB+XGB+ET)</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.972213949210214</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.01313712138486632</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.555579079125358</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.3169052687879627</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2.460410412719198</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.5677983162702932</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.6681835378861795</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.1157007691251278</v>
+      </c>
+      <c r="J6" t="n">
+        <v>5.494119106912052</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.6444601836087989</v>
+      </c>
+      <c r="L6" t="n">
+        <v>7.928452692086688</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.290375076439692</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.6868710356890655</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.1049558606881848</v>
+      </c>
+      <c r="P6" t="n">
+        <v>5.616395416283747</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.6373650560579993</v>
+      </c>
+      <c r="R6" t="n">
+        <v>8.090723708996862</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.315398253175329</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.2853429135211485</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>engineered_9</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>random_5x5</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>BoostStack(GB+LGBM+CB+XGB+ET)</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.9532334851005707</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.01778065532614966</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.156640843774983</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.3999664453629337</v>
+      </c>
+      <c r="F7" t="n">
+        <v>3.075328661789021</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.570882257860327</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.5352304303066695</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.09644446176633339</v>
+      </c>
+      <c r="J7" t="n">
+        <v>7.378010606681964</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.8750392140401001</v>
+      </c>
+      <c r="L7" t="n">
+        <v>10.47887793052915</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.612587106700538</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.5079491173517063</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.1280531208203537</v>
+      </c>
+      <c r="P7" t="n">
+        <v>6.996922278444751</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.087025090858577</v>
+      </c>
+      <c r="R7" t="n">
+        <v>10.2026536284075</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.097312171579741</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.4452843677488644</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>engineered_9</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>GroupKFold</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>GB_seed_ensemble(10)</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.9925604114406019</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.00230910266160749</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.6844729360211257</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.1036021192513047</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1.286710096285147</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.2107823253963939</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.648693392863039</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.1215427393490926</v>
+      </c>
+      <c r="J8" t="n">
+        <v>5.560061591711149</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.7014389229536119</v>
+      </c>
+      <c r="L8" t="n">
+        <v>8.14475088417778</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.31605018005552</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.6729361468467839</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.1078180284339218</v>
+      </c>
+      <c r="P8" t="n">
+        <v>5.697509580986122</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.6711571904050936</v>
+      </c>
+      <c r="R8" t="n">
+        <v>8.286755622931075</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.326826574496561</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.319624264593818</v>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>engineered_9</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>random_5x5</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>GB_seed_ensemble(10)</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.9906070255693644</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.002518804465338614</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.7190789451629811</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.09101079392908416</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.393344972669341</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.2004654855557588</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.4594241464199661</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.1215284770718606</v>
+      </c>
+      <c r="J9" t="n">
+        <v>8.057974208169615</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1.288209132982426</v>
+      </c>
+      <c r="L9" t="n">
+        <v>11.29034916708354</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.802678592904553</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.4770206388730996</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.1039690922968273</v>
+      </c>
+      <c r="P9" t="n">
+        <v>7.326525459690271</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.9970699550210352</v>
+      </c>
+      <c r="R9" t="n">
+        <v>10.53667341598648</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.855875904231499</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.5135863866962649</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>engineered_9</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>GroupKFold</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G43"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>feature_set</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>protocol</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>test_r2</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>test_r2_std</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>train_r2</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>overfit_gap</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Gradient Boosting</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>engineered_12</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>LOOCV</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0.7942633316576376</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.9953556886724756</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.201092357014838</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>BoostStack</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>engineered_12</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>LOOCV</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0.7924010722448531</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.98162376060449</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.1892226883596368</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>GB_seed_ensemble(10)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>engineered_12</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>LOOCV</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0.7793604854771845</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9956685814305508</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.2163080959533663</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>BoostStack</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>engineered_9</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>LOOCV</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0.7736850350049765</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.9742867457741047</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.2006017107691281</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>engineered_12</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>LOOCV</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0.7685170039975291</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.9928695470653107</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.2243525430677816</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>GB_seed_ensemble(10)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>engineered_9</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>LOOCV</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0.7667364821944499</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.9884544530743798</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.2217179708799299</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ExtraTrees</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>engineered_9</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>LOOCV</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0.7654595269411394</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.9372501483598261</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.1717906214186867</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>CatBoost</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="n">
-        <v>0.4687322912180187</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.3051480295997313</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>ElasticNet</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="n">
-        <v>1.312899313230605e+19</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.1028482075217156</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>engineered_12</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>LOOCV</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.7654201837864745</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.9710704058607644</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.20565022207429</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>LightGBM</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>engineered_9</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>LOOCV</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0.7625690759284813</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.9716315459698326</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.2090624700413513</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>ExtraTrees</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>0.4328042284986798</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0.2714878689266054</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0.4328042284986798</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0.2677131869698117</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>GaussianProcess</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="n">
-        <v>0.5172882038448935</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0.274770251912596</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>engineered_12</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>LOOCV</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0.751856186271981</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.9153187222080731</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.1634625359360921</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>LightGBM</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>engineered_12</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>LOOCV</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0.7514959501031634</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.9574331485512623</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.2059371984480989</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Gradient Boosting</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="n">
-        <v>0.5088347519071406</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0.3185172823434543</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>HistGradientBoosting</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>0.5326476795895159</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.3279270342135067</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.5326476795895159</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.3335776325066149</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>KNN</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="n">
-        <v>0.6007135677473598</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0.3835444864480727</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>Lasso</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="n">
-        <v>2.601593224341503e+19</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0.106280462997139</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>engineered_9</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>LOOCV</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0.7503071117321556</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.9881199212446891</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.2378128095125335</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>BoostStack</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>engineered_12</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>10-fold x10</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0.7494088929353109</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.1223173180744844</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.9791951854847687</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.2297862925494578</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>GB_seed_ensemble(10)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>engineered_12</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>10-fold x10</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0.7443392003640767</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.122453294321198</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.9960694774206454</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.2517302770565687</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>BoostStack</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>engineered_9</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>10-fold x10</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>0.7429193350301786</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.1259883658820705</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.9740128407219001</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.2310935056917215</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>engineered_9</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>LOOCV</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>0.7418589645557747</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.9828880379136228</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.2410290733578481</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>BoostStack</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>engineered_12</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>5-fold x20</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>0.7405991798508234</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.08316383834984797</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.9751248855319166</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.2345257056810932</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Gradient Boosting</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>engineered_12</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>10-fold x10</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>0.7374546950804934</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.1266179992926218</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.9959213739129302</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.2584666788324368</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>GB_seed_ensemble(10)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>engineered_12</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>5-fold x20</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>0.7320424095253112</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.08504089716102334</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.9964965432626011</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.2644541337372899</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>BoostStack</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>engineered_9</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>5-fold x20</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>0.7319940959850086</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.08550101630978657</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.9728133118259912</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.2408192158409825</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>ExtraTrees</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>engineered_9</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>10-fold x10</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>0.7305597791379208</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.1203213150093167</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.9416332038686649</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.2110734247307441</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>GB_seed_ensemble(10)</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>engineered_9</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>10-fold x10</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>0.7301027996738993</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.1335678079164369</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.9892675239450215</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.2591647242711221</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>engineered_12</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>10-fold x10</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>0.7296152818950461</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.1159801360652022</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.9926787167184375</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.2630634348233915</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Gradient Boosting</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>engineered_12</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>5-fold x20</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>0.7279680359742666</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.08422567421360341</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.9963737331748064</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.2684056972005398</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>CatBoost</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>engineered_12</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>10-fold x10</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>0.7260694923350094</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.1259503180719752</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.9748119798783266</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.2487424875433172</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ExtraTrees</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>engineered_9</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>5-fold x20</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>0.7239447065196505</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.08301244872933647</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.9469827344405527</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.2230380279209022</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>ExtraTrees</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>engineered_12</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>10-fold x10</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>0.721403504109844</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.1215500610801326</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.9214527571172775</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.2000492530074335</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
         <is>
           <t>LightGBM</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="n">
-        <v>0.5299237110508204</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0.3064172251990254</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>PLS</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="n">
-        <v>1.017337186779134e+17</v>
-      </c>
-      <c r="E13" t="n">
-        <v>5.28110644844545e+18</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>Random Forest</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="n">
-        <v>0.4979199756819547</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0.3148520477845754</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>Ridge</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="n">
-        <v>3.651176760113215e+19</v>
-      </c>
-      <c r="E15" t="n">
-        <v>2.614720185200482e+18</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>Ridge+Poly</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="n">
-        <v>9.844493573592266e+16</v>
-      </c>
-      <c r="E16" t="n">
-        <v>3.560642177403972e+19</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>SVR_RBF</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>0.3378088467588833</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0.2272273776158613</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0.3300247590638997</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0.2128511609186781</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>Stacked (SVR+ET+XGB+HGB)</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="n">
-        <v>0.3986036864761409</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0.2501489640860096</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>engineered_9</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>10-fold x10</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>0.7197174690694293</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.1403765701392258</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.9732676490447574</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.253550179975328</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>ExtraTrees</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>engineered_12</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>5-fold x20</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>0.7165454259936739</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.08256975085287828</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.9258167674825996</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.2092713414889257</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>CatBoost</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>engineered_12</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>5-fold x20</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>0.7152529739217858</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.08594245141175323</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.9779911457150169</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.2627381717932311</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>GB_seed_ensemble(10)</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>engineered_9</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>5-fold x20</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>0.7151122666647289</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.08957767169741786</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.9902979856000705</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.2751857189353416</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Gradient Boosting</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>engineered_9</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>10-fold x10</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>0.714904717321742</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.1391562845877351</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.9888930383717343</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.2739883210499923</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>LightGBM</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>engineered_12</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>10-fold x10</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>0.7147975143297025</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.1310822295304845</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.9608381625520777</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.2460406482223751</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
         <is>
           <t>XGBoost</t>
         </is>
       </c>
-      <c r="B19" t="n">
-        <v>0.5810605947383944</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0.3222792443272965</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0.5646169794241067</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0.3317645837736818</v>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>engineered_12</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>5-fold x20</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>0.708470040093648</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.08631609287602299</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.9922917605046894</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.2838217204110414</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>engineered_9</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>10-fold x10</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>0.7071923541815147</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.1298577484642606</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.9829601586332702</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.2757678044517555</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>CatBoost</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>engineered_9</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>LOOCV</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>0.7052673929925758</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.8928016239574877</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.187534230964912</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Gradient Boosting</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>engineered_9</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>5-fold x20</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>0.7051469601315427</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.09230782907608795</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.9899621042862649</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.2848151441547222</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>LightGBM</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>engineered_12</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>5-fold x20</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>0.7021282166375273</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.09193540343364512</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.9643341355408573</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.26220591890333</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>LightGBM</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>engineered_9</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>5-fold x20</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>0.7011909195131143</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.09446197497336152</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.975606553999247</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.2744156344861327</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>engineered_9</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>5-fold x20</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>0.6916930565673988</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.08815573668137233</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.9828150500321436</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0.2911219934647449</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>CatBoost</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>engineered_9</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>10-fold x10</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>0.6619148503863193</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.1439862506306333</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0.8961834897961671</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0.2342686394098479</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>CatBoost</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>engineered_9</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>5-fold x20</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>0.6526719283299723</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.09581758704992951</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0.9015342785201311</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0.2488623501901588</v>
       </c>
     </row>
   </sheetData>
@@ -11149,6 +14150,1077 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>experiment</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>feature_set</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>protocol</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>test_r2</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>train_r2</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>overfit_gap</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>wide_stack</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>WideStack(8bases)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>engineered_12</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>LOOCV</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>0.7970576212430787</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.9747500563085396</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.177692435065461</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>enet_meta</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>BoostStack_ElasticMeta</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>engineered_12</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LOOCV</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>0.7848053657822631</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.9743073476470062</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.1895019818647431</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>tight_optuna</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Gradient Boosting_300trials</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>engineered_12</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LOOCV</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>0.7753144127238004</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9929643929855446</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.2176499802617442</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>wide_stack</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>WideStack(8bases)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>engineered_9</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LOOCV</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>0.7720011972860561</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.9661870875160439</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.1941858902299878</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>enet_meta</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>BoostStack_ElasticMeta</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>engineered_9</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LOOCV</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>0.7687112155591823</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.9662042361005007</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.1974930205413183</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>tight_optuna</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>XGBoost_300trials</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>engineered_12</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LOOCV</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>0.760354122801059</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.9860771014987689</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.22572297869771</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>SMOGN_group</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>SMOGN_random</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>group_strict</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>random_KF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>AdaBoost</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="n">
+        <v>0.2424954348431182</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.463419019492389</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>BayesianRidge</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="n">
+        <v>-1.025208226003857e+20</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-1.301642117577251e+19</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>BoostStack(GB+LGBM+CB+XGB+ET)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="n">
+        <v>0.5165052899329102</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.7013662369195868</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>CatBoost</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="n">
+        <v>0.518685299246141</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.6800005703790878</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>ElasticNet</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="n">
+        <v>-1.312899313230605e+19</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.2443330070411298</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>ExtraTrees</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.5120134711810558</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.6750008760063723</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.5273940608703354</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.6848263248813695</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>GB_seed_ensemble(10)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="n">
+        <v>0.4770206388730996</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.6932082172344949</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>GaussianProcess</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="n">
+        <v>0.4152400171443699</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.5935778340706519</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Gradient Boosting</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="n">
+        <v>0.4814603090734479</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.6789381943992349</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>HistGradientBoosting</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.4281417063439478</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.6481401309935099</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.4281417063439478</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.6418195140439492</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>KNN</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="n">
+        <v>0.393041828052859</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.6164364310788732</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Lasso</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="n">
+        <v>-2.601593224341503e+19</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.240953414114923</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>LightGBM</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="n">
+        <v>0.4438988428388094</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.6655718460950149</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>MLP</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="n">
+        <v>0.3355019483982192</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.511053070156766</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>MLP_group_obj</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="n">
+        <v>0.3355019483982192</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.511053070156766</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>MLP_random_obj</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="n">
+        <v>0.5112760340309848</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.592881926832985</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>MLP_seed_ensemble</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="n">
+        <v>0.5194617222325817</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.6323349391106788</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>PLS</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="n">
+        <v>-1.017337186779134e+17</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-5.28110644844545e+18</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Random Forest</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="n">
+        <v>0.4322458312992719</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.626259917054957</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>Ridge</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="n">
+        <v>-3.651176760113215e+19</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-2.614720185200482e+18</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Ridge+Poly</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="n">
+        <v>-9.844493573592266e+16</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-3.560642177403972e+19</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>SVR_RBF</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>0.4727678796962161</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.559565778843728</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.5235726680511263</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.6137629940723229</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>Stacked (SVR+ET+XGB+HGB)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="n">
+        <v>0.5212331659450371</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.7030189472874318</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>0.4103448982353368</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.670262647318171</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.4174013507683088</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.6604985786262069</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>SMOGN_group</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>SMOGN_random</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>group_strict</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>random_KF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>AdaBoost</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="n">
+        <v>0.4664312091133778</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.2363304310683094</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>BayesianRidge</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="n">
+        <v>1.025208226003857e+20</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1.301642117577251e+19</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>BoostStack(GB+LGBM+CB+XGB+ET)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="n">
+        <v>0.4333827615362446</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.268065416495005</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>CatBoost</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="n">
+        <v>0.4687322912180187</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.3051480295997313</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>ElasticNet</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="n">
+        <v>1.312899313230605e+19</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.1028482075217156</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>ExtraTrees</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.4335499898427331</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.2595553352470881</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.4395173328969032</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.2724155429586185</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>GB_seed_ensemble(10)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="n">
+        <v>0.5135863866962649</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.3043911601670625</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>GaussianProcess</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="n">
+        <v>0.509873042145528</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.3042407189115824</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Gradient Boosting</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="n">
+        <v>0.5088347519071406</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.3185172823434543</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>HistGradientBoosting</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.5410588346781695</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.3198398348049419</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.5410588346781695</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.3271089788555652</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>KNN</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="n">
+        <v>0.6007135677473598</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.3835444864480727</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Lasso</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="n">
+        <v>2.601593224341503e+19</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.106280462997139</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>LightGBM</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="n">
+        <v>0.5299237110508204</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.3064172251990254</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>MLP</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="n">
+        <v>0.6466512193087257</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.4642880496411907</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>MLP_group_obj</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="n">
+        <v>0.6466512193087257</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.4642880496411907</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>MLP_random_obj</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="n">
+        <v>0.4527604891454311</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.3536121037847779</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>MLP_seed_ensemble</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="n">
+        <v>0.4482602613272673</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.3483609764867092</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>PLS</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="n">
+        <v>1.017337186779134e+17</v>
+      </c>
+      <c r="E19" t="n">
+        <v>5.28110644844545e+18</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Random Forest</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="n">
+        <v>0.4979199756819547</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.3148520477845754</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>Ridge</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="n">
+        <v>3.651176760113215e+19</v>
+      </c>
+      <c r="E21" t="n">
+        <v>2.614720185200482e+18</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Ridge+Poly</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="n">
+        <v>9.844493573592266e+16</v>
+      </c>
+      <c r="E22" t="n">
+        <v>3.560642177403972e+19</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>SVR_RBF</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>0.3378088467588833</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.2272273776158613</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.3300247590638997</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.2128511609186781</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>Stacked (SVR+ET+XGB+HGB)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="n">
+        <v>0.3917501802409054</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.2432718238056022</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>0.5810605947383944</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.3222792443272965</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.5646169794241067</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.3317645837736818</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
